--- a/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
+++ b/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
@@ -8,18 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\realestate\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1BA161-E22B-4D13-B95A-B0F05207AC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B3EE1F-670D-4A15-8329-DB637D2C1EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
   </bookViews>
   <sheets>
-    <sheet name="Conguagli spese" sheetId="1" r:id="rId1"/>
-    <sheet name="Conguagli spese Prorata" sheetId="3" r:id="rId2"/>
+    <sheet name="Conguagli spese" sheetId="4" r:id="rId1"/>
+    <sheet name="Conguagli spese Pro-rata" sheetId="5" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Conguagli spese'!$A$1:$G$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Conguagli spese Prorata'!$A$1:$G$30</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -158,10 +154,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-  </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,43 +171,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -226,21 +185,7 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -251,7 +196,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -259,417 +204,212 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="6">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
+        <strike val="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <strike val="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF7C2C1"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF7C2C1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-410]_-;\-* #,##0.00\ [$€-410]_-;_-* &quot;-&quot;??\ [$€-410]_-;_-@_-"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -687,88 +427,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EDFFC5C-15BA-41C1-A573-16895C48713E}" name="Tabella1" displayName="Tabella1" ref="A13:G26" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
-  <autoFilter ref="A13:G26" xr:uid="{7EDFFC5C-15BA-41C1-A573-16895C48713E}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{2C273954-DE9B-4C1A-906F-88F1A8DE2F4E}" name="Spesa da ripartire" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{BDDF30DA-1A34-4AFE-8AC9-C4A5002891E6}" name="Totale" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{48D01DED-AE88-46F7-B2D3-DC7AC7D698CD}" name="Tipo" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{CE2FA730-DC58-45E1-9E24-8CCE45FCA81E}" name="App. 1" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{1D501B41-CE35-4E48-95E4-C930E890E131}" name="App. 2" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{E0C2268A-4D14-4007-8F39-4AB92F348C25}" name="App. 3" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{687F9840-998B-484E-9F28-0E94F3AD28F1}" name="Differenze" dataDxfId="26">
-      <calculatedColumnFormula>$D14+$E14+$F14</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{ED44A568-E591-4A3F-8D96-40674BA9CBE3}" name="Tabella4" displayName="Tabella4" ref="A5:E11" totalsRowShown="0">
-  <autoFilter ref="A5:E11" xr:uid="{ED44A568-E591-4A3F-8D96-40674BA9CBE3}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5FA9E7D7-202A-4E1B-A634-5C928F0C3DAF}" name="Tipo di ripartizione"/>
-    <tableColumn id="2" xr3:uid="{4E129D9F-4224-42E4-8173-09095C270A85}" name="App. 1" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{3B657F5C-AD36-496B-A58B-91D0FD74D940}" name="App. 2" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{D6EAECB3-C7DE-4270-B914-0A6ADB3BB4CC}" name="App. 3" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{7665926A-4646-456B-86BD-949B4CBD1F07}" name="Totale" dataDxfId="22"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B7A3B0EE-106B-4B90-B5E1-1AA1E2049F05}" name="Tabella16" displayName="Tabella16" ref="A13:G26" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A13:G26" xr:uid="{7EDFFC5C-15BA-41C1-A573-16895C48713E}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D980C600-50FF-40F9-BA9C-D627D7865C47}" name="Spesa da ripartire" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{800094BF-7326-49B9-804B-F0FB019EFF2B}" name="Totale" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{ADAF8785-5238-4735-B68D-F636B79D2698}" name="Tipo" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{018A85E4-D150-48B6-9349-5E22EF00FC19}" name="App. 1" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{23A79678-9C2C-4CB8-9AF7-874990569583}" name="App. 2" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{6D2AAAD5-E835-4FC4-9E3F-E269F9616D9C}" name="App. 3" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{2C370E16-C2F9-4889-B618-1E8D4B554027}" name="Differenze" dataDxfId="13">
-      <calculatedColumnFormula>$B14-SUM($D14:$F14)</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A3E937DA-C300-455F-B7AC-4A45B5479E6F}" name="Tabella47" displayName="Tabella47" ref="A5:E11" totalsRowShown="0">
-  <autoFilter ref="A5:E11" xr:uid="{ED44A568-E591-4A3F-8D96-40674BA9CBE3}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8F561E8B-0447-4EB2-AC66-B959F54EBCE2}" name="Tipo di ripartizione"/>
-    <tableColumn id="2" xr3:uid="{A0E5C9C8-BBDB-4BF4-AB4E-F52AC1849A5A}" name="App. 1" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{78B3AF80-8C2C-4447-8414-98145F740A7A}" name="App. 2" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{35612B7F-D41C-4095-B625-48DB7F64DC91}" name="App. 3" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{FF9F06AC-F1DC-41CF-92A3-0CFFF00AC785}" name="Totale" dataDxfId="9"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{26D98444-E718-4DAF-A732-FD0A8C45901A}" name="Tabella7" displayName="Tabella7" ref="A28:E30" totalsRowShown="0">
-  <autoFilter ref="A28:E30" xr:uid="{26D98444-E718-4DAF-A732-FD0A8C45901A}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{069F6DA9-4A71-4C57-8936-857FEA86101B}" name="Calcolo prorata"/>
-    <tableColumn id="2" xr3:uid="{253E7923-15EA-4A25-9E0B-638EE573F3C5}" name="Mesi"/>
-    <tableColumn id="3" xr3:uid="{E3B9E5FA-5EB4-44B2-A828-0829F24A0EDC}" name="App. 3" dataDxfId="8">
-      <calculatedColumnFormula>$F$24/12*2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{93F33975-3E35-400B-92D7-133D1D932083}" name="Acconto" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{AE0B9D65-B077-40B5-A771-D68274EB1147}" name="Conguaglio" dataDxfId="6">
-      <calculatedColumnFormula>$C29+$D29</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1087,27 +745,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD82E2A4-2D0C-4E27-8A01-B72A4F39E833}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9073075C-C130-45EE-B2DF-A3C8E1CA77C7}">
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.88671875" customWidth="1"/>
+    <col min="2" max="3" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1120,547 +767,546 @@
       <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="2">
         <v>45292</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="2">
         <v>45657</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-    </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="E5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="F5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="G5" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="12">
         <v>200</v>
       </c>
-      <c r="C6" s="23">
+      <c r="E6" s="9">
         <v>300</v>
       </c>
-      <c r="D6" s="23">
+      <c r="F6" s="9">
         <v>500</v>
       </c>
-      <c r="E6" s="24">
-        <f>SUM($B6:$D6)</f>
+      <c r="G6" s="9">
+        <f>SUM($D6:$F6)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="17"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="12">
         <v>54</v>
       </c>
-      <c r="C7" s="13">
+      <c r="E7" s="9">
         <v>85</v>
       </c>
-      <c r="D7" s="13">
+      <c r="F7" s="9">
         <v>124</v>
       </c>
-      <c r="E7" s="13">
-        <f>SUM($B7:$D7)</f>
+      <c r="G7" s="9">
+        <f>SUM($D7:$F7)</f>
         <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="17"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="12">
         <v>10241</v>
       </c>
-      <c r="C8" s="13">
+      <c r="E8" s="9">
         <v>13400</v>
       </c>
-      <c r="D8" s="13">
+      <c r="F8" s="9">
         <v>22578</v>
       </c>
-      <c r="E8" s="13">
-        <f>SUM($B8:$D8)</f>
+      <c r="G8" s="9">
+        <f>SUM($D8:$F8)</f>
         <v>46219</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="12">
         <v>1104</v>
       </c>
-      <c r="C9" s="13">
+      <c r="E9" s="9">
         <v>1210</v>
       </c>
-      <c r="D9" s="13">
+      <c r="F9" s="9">
         <v>1898</v>
       </c>
-      <c r="E9" s="13">
-        <f>SUM($B9:$D9)</f>
+      <c r="G9" s="9">
+        <f>SUM($D9:$F9)</f>
         <v>4212</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="17"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="12">
         <v>1</v>
       </c>
-      <c r="C10" s="13">
+      <c r="E10" s="9">
         <v>1</v>
       </c>
-      <c r="D10" s="13">
+      <c r="F10" s="9">
         <v>1</v>
       </c>
-      <c r="E10" s="13">
-        <f>SUM($B10:$D10)</f>
+      <c r="G10" s="9">
+        <f>SUM($D10:$F10)</f>
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-    </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="4">
+      <c r="A14" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="13">
         <v>4000</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="5">
-        <f>$B14/$E$8*$B$8</f>
+      <c r="D14" s="13">
+        <f>$B14/$G$8*$D$8</f>
         <v>886.30217010320439</v>
       </c>
-      <c r="E14" s="5">
-        <f>$B14/$E$8*$C$8</f>
+      <c r="E14" s="13">
+        <f>$B14/$G$8*$E$8</f>
         <v>1159.6962288236441</v>
       </c>
-      <c r="F14" s="5">
-        <f>$B14/$E$8*$D$8</f>
+      <c r="F14" s="13">
+        <f>$B14/$G$8*$F$8</f>
         <v>1954.0016010731517</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="13">
         <f>$B14-SUM($D14:$F14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="13">
         <v>2000</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="5">
-        <f>$B15/$E$6*$B$6</f>
+      <c r="D15" s="13">
+        <f>$B15/$G$6*$D$6</f>
         <v>400</v>
       </c>
-      <c r="E15" s="5">
-        <f>$B15/$E$6*$C$6</f>
+      <c r="E15" s="13">
+        <f>$B15/$G$6*$E$6</f>
         <v>600</v>
       </c>
-      <c r="F15" s="5">
-        <f>$B15/$E$6*$D$6</f>
+      <c r="F15" s="13">
+        <f>$B15/$G$6*$F$6</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="13">
         <f t="shared" ref="G15:G26" si="0">$B15-SUM($D15:$F15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="13">
         <v>200</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="5">
-        <f>$B16/$E$6*$B$6</f>
+      <c r="D16" s="13">
+        <f>$B16/$G$6*$D$6</f>
         <v>40</v>
       </c>
-      <c r="E16" s="5">
-        <f t="shared" ref="E16:E19" si="1">$B16/$E$6*$C$6</f>
+      <c r="E16" s="13">
+        <f>$B16/$G$6*$E$6</f>
         <v>60</v>
       </c>
-      <c r="F16" s="5">
-        <f t="shared" ref="F16:F19" si="2">$B16/$E$6*$D$6</f>
+      <c r="F16" s="13">
+        <f>$B16/$G$6*$F$6</f>
         <v>100</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="13">
         <v>50</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="5">
-        <f t="shared" ref="D17:D19" si="3">$B17/$E$6*$B$6</f>
+      <c r="D17" s="13">
+        <f>$B17/$G$6*$D$6</f>
         <v>10</v>
       </c>
-      <c r="E17" s="5">
-        <f t="shared" si="1"/>
+      <c r="E17" s="13">
+        <f>$B17/$G$6*$E$6</f>
         <v>15</v>
       </c>
-      <c r="F17" s="5">
-        <f t="shared" si="2"/>
+      <c r="F17" s="13">
+        <f>$B17/$G$6*$F$6</f>
         <v>25</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="13">
         <v>800</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="5">
-        <f t="shared" si="3"/>
+      <c r="D18" s="13">
+        <f>$B18/$G$6*$D$6</f>
         <v>160</v>
       </c>
-      <c r="E18" s="5">
-        <f t="shared" si="1"/>
+      <c r="E18" s="13">
+        <f>$B18/$G$6*$E$6</f>
         <v>240</v>
       </c>
-      <c r="F18" s="5">
-        <f t="shared" si="2"/>
+      <c r="F18" s="13">
+        <f>$B18/$G$6*$F$6</f>
         <v>400</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="13">
         <v>300</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="5">
-        <f t="shared" si="3"/>
+      <c r="D19" s="13">
+        <f>$B19/$G$6*$D$6</f>
         <v>60</v>
       </c>
-      <c r="E19" s="5">
-        <f t="shared" si="1"/>
+      <c r="E19" s="13">
+        <f>$B19/$G$6*$E$6</f>
         <v>90</v>
       </c>
-      <c r="F19" s="5">
-        <f t="shared" si="2"/>
+      <c r="F19" s="13">
+        <f>$B19/$G$6*$F$6</f>
         <v>150</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="13">
         <v>400</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="5">
-        <f>$B20/$E$9*$B$9</f>
+      <c r="D20" s="13">
+        <f>$B20/$G$9*$D$9</f>
         <v>104.84330484330485</v>
       </c>
-      <c r="E20" s="5">
-        <f>$B20/$E$9*$C$9</f>
+      <c r="E20" s="13">
+        <f>$B20/$G$9*$E$9</f>
         <v>114.90978157644825</v>
       </c>
-      <c r="F20" s="5">
-        <f>$B20/$E$9*$D$9</f>
+      <c r="F20" s="13">
+        <f>$B20/$G$9*$F$9</f>
         <v>180.24691358024694</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="13">
         <v>500</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="5">
-        <f>$B21/$E$6*$B$6</f>
+      <c r="D21" s="13">
+        <f>$B21/$G$6*$D$6</f>
         <v>100</v>
       </c>
-      <c r="E21" s="5">
-        <f>$B21/$E$6*$C$6</f>
+      <c r="E21" s="13">
+        <f>$B21/$G$6*$E$6</f>
         <v>150</v>
       </c>
-      <c r="F21" s="5">
-        <f>$B21/$E$6*$D$6</f>
+      <c r="F21" s="13">
+        <f>$B21/$G$6*$F$6</f>
         <v>250</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="13">
         <v>100</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="5">
-        <f>$B22/$E$6*$B$6</f>
+      <c r="D22" s="13">
+        <f>$B22/$G$6*$D$6</f>
         <v>20</v>
       </c>
-      <c r="E22" s="5">
-        <f>$B22/$E$6*$C$6</f>
+      <c r="E22" s="13">
+        <f>$B22/$G$6*$E$6</f>
         <v>30</v>
       </c>
-      <c r="F22" s="5">
-        <f>$B22/$E$6*$D$6</f>
+      <c r="F22" s="13">
+        <f>$B22/$G$6*$F$6</f>
         <v>50</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="13">
         <v>1250</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="5">
-        <f>$B23/$E$10*$B$10</f>
+      <c r="D23" s="13">
+        <f>$B23/$G$10*$D$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="E23" s="5">
-        <f>$B23/$E$10*$C$10</f>
+      <c r="E23" s="13">
+        <f>$B23/$G$10*$E$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="F23" s="5">
-        <f>$B23/$E$10*$D$10</f>
+      <c r="F23" s="13">
+        <f>$B23/$G$10*$F$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="G23" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
+      <c r="G23" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="14">
         <f>SUBTOTAL(109,B14:B23)</f>
         <v>9600</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16">
+      <c r="C24" s="19"/>
+      <c r="D24" s="14">
         <f>SUBTOTAL(109,D14:D23)</f>
         <v>2197.8121416131758</v>
       </c>
-      <c r="E24" s="16">
-        <f t="shared" ref="E24:F24" si="4">SUBTOTAL(109,E14:E23)</f>
+      <c r="E24" s="14">
+        <f t="shared" ref="E24:F24" si="1">SUBTOTAL(109,E14:E23)</f>
         <v>2876.2726770667587</v>
       </c>
-      <c r="F24" s="16">
-        <f t="shared" si="4"/>
+      <c r="F24" s="14">
+        <f t="shared" si="1"/>
         <v>4525.9151813200651</v>
       </c>
-      <c r="G24" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="G24" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="15">
         <f>SUM($D25:$F25)</f>
         <v>-9200</v>
       </c>
-      <c r="D25" s="7">
+      <c r="C25" s="20"/>
+      <c r="D25" s="15">
         <v>-2000</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="15">
         <v>-3000</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="15">
         <v>-4200</v>
       </c>
-      <c r="G25" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="G25" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="13">
         <f>SUM($D26:$F26)</f>
         <v>399.99999999999955</v>
       </c>
-      <c r="D26" s="9">
+      <c r="C26" s="21"/>
+      <c r="D26" s="13">
         <f>$D24+$D25</f>
         <v>197.81214161317575</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="13">
         <f>$E24+$E25</f>
         <v>-123.72732293324134</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="13">
         <f>$F24+$F25</f>
         <v>325.91518132006513</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <mergeCells count="8">
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+  </mergeCells>
   <conditionalFormatting sqref="D26:F26">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="G14:G26" calculatedColumn="1"/>
-    <ignoredError sqref="D20:F20" formula="1"/>
-  </ignoredErrors>
-  <tableParts count="2">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B029749-BA36-4C12-8B1C-4D1814EDCC2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEEC9161-9944-4F33-924D-68E41F754380}">
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" customWidth="1"/>
+    <col min="2" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1673,580 +1319,593 @@
       <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="2">
         <v>45292</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="2">
         <v>45657</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-    </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="E5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="F5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="G5" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="9">
         <v>200</v>
       </c>
-      <c r="C6" s="23">
+      <c r="E6" s="9">
         <v>300</v>
       </c>
-      <c r="D6" s="23">
+      <c r="F6" s="9">
         <v>500</v>
       </c>
-      <c r="E6" s="24">
-        <f>SUM($B6:$D6)</f>
+      <c r="G6" s="9">
+        <f>SUM($D6:$F6)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="17"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="9">
         <v>54</v>
       </c>
-      <c r="C7" s="13">
+      <c r="E7" s="9">
         <v>85</v>
       </c>
-      <c r="D7" s="13">
+      <c r="F7" s="9">
         <v>124</v>
       </c>
-      <c r="E7" s="13">
-        <f>SUM($B7:$D7)</f>
+      <c r="G7" s="9">
+        <f>SUM($D7:$F7)</f>
         <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="17"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="9">
         <v>10241</v>
       </c>
-      <c r="C8" s="13">
+      <c r="E8" s="9">
         <v>13400</v>
       </c>
-      <c r="D8" s="13">
+      <c r="F8" s="9">
         <v>22578</v>
       </c>
-      <c r="E8" s="13">
-        <f>SUM($B8:$D8)</f>
+      <c r="G8" s="9">
+        <f>SUM($D8:$F8)</f>
         <v>46219</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="9">
         <v>1104</v>
       </c>
-      <c r="C9" s="13">
+      <c r="E9" s="9">
         <v>1210</v>
       </c>
-      <c r="D9" s="13">
+      <c r="F9" s="9">
         <v>1898</v>
       </c>
-      <c r="E9" s="13">
-        <f>SUM($B9:$D9)</f>
+      <c r="G9" s="9">
+        <f>SUM($D9:$F9)</f>
         <v>4212</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="17"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="9">
         <v>1</v>
       </c>
-      <c r="C10" s="13">
+      <c r="E10" s="9">
         <v>1</v>
       </c>
-      <c r="D10" s="13">
+      <c r="F10" s="9">
         <v>1</v>
       </c>
-      <c r="E10" s="13">
-        <f>SUM($B10:$D10)</f>
+      <c r="G10" s="9">
+        <f>SUM($D10:$F10)</f>
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-    </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="4">
+      <c r="A14" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="13">
         <v>4000</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="5">
-        <f>$B14/$E$8*$B$8</f>
+      <c r="D14" s="13">
+        <f>$B14/$G$8*$D$8</f>
         <v>886.30217010320439</v>
       </c>
-      <c r="E14" s="5">
-        <f>$B14/$E$8*$C$8</f>
+      <c r="E14" s="13">
+        <f>$B14/$G$8*$E$8</f>
         <v>1159.6962288236441</v>
       </c>
-      <c r="F14" s="5">
-        <f>$B14/$E$8*$D$8</f>
+      <c r="F14" s="13">
+        <f>$B14/$G$8*$F$8</f>
         <v>1954.0016010731517</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="13">
         <f>$B14-SUM($D14:$F14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="13">
         <v>2000</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="5">
-        <f>$B15/$E$6*$B$6</f>
+      <c r="D15" s="13">
+        <f>$B15/$G$6*$D$6</f>
         <v>400</v>
       </c>
-      <c r="E15" s="5">
-        <f>$B15/$E$6*$C$6</f>
+      <c r="E15" s="13">
+        <f>$B15/$G$6*$E$6</f>
         <v>600</v>
       </c>
-      <c r="F15" s="5">
-        <f>$B15/$E$6*$D$6</f>
+      <c r="F15" s="13">
+        <f>$B15/$G$6*$F$6</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="13">
         <f t="shared" ref="G15:G26" si="0">$B15-SUM($D15:$F15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="13">
         <v>200</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="5">
-        <f>$B16/$E$6*$B$6</f>
+      <c r="D16" s="13">
+        <f>$B16/$G$6*$D$6</f>
         <v>40</v>
       </c>
-      <c r="E16" s="5">
-        <f t="shared" ref="E16:E19" si="1">$B16/$E$6*$C$6</f>
+      <c r="E16" s="13">
+        <f>$B16/$G$6*$E$6</f>
         <v>60</v>
       </c>
-      <c r="F16" s="5">
-        <f t="shared" ref="F16:F19" si="2">$B16/$E$6*$D$6</f>
+      <c r="F16" s="13">
+        <f>$B16/$G$6*$F$6</f>
         <v>100</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="13">
         <v>50</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="5">
-        <f t="shared" ref="D17:D19" si="3">$B17/$E$6*$B$6</f>
+      <c r="D17" s="13">
+        <f>$B17/$G$6*$D$6</f>
         <v>10</v>
       </c>
-      <c r="E17" s="5">
-        <f t="shared" si="1"/>
+      <c r="E17" s="13">
+        <f>$B17/$G$6*$E$6</f>
         <v>15</v>
       </c>
-      <c r="F17" s="5">
-        <f t="shared" si="2"/>
+      <c r="F17" s="13">
+        <f>$B17/$G$6*$F$6</f>
         <v>25</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="13">
         <v>800</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="5">
-        <f t="shared" si="3"/>
+      <c r="D18" s="13">
+        <f>$B18/$G$6*$D$6</f>
         <v>160</v>
       </c>
-      <c r="E18" s="5">
-        <f t="shared" si="1"/>
+      <c r="E18" s="13">
+        <f>$B18/$G$6*$E$6</f>
         <v>240</v>
       </c>
-      <c r="F18" s="5">
-        <f t="shared" si="2"/>
+      <c r="F18" s="13">
+        <f>$B18/$G$6*$F$6</f>
         <v>400</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="13">
         <v>300</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="5">
-        <f t="shared" si="3"/>
+      <c r="D19" s="13">
+        <f>$B19/$G$6*$D$6</f>
         <v>60</v>
       </c>
-      <c r="E19" s="5">
-        <f t="shared" si="1"/>
+      <c r="E19" s="13">
+        <f>$B19/$G$6*$E$6</f>
         <v>90</v>
       </c>
-      <c r="F19" s="5">
-        <f t="shared" si="2"/>
+      <c r="F19" s="13">
+        <f>$B19/$G$6*$F$6</f>
         <v>150</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="13">
         <v>400</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="5">
-        <f>$B20/$E$9*$B$9</f>
+      <c r="D20" s="13">
+        <f>$B20/$G$9*$D$9</f>
         <v>104.84330484330485</v>
       </c>
-      <c r="E20" s="5">
-        <f>$B20/$E$9*$C$9</f>
+      <c r="E20" s="13">
+        <f>$B20/$G$9*$E$9</f>
         <v>114.90978157644825</v>
       </c>
-      <c r="F20" s="5">
-        <f>$B20/$E$9*$D$9</f>
+      <c r="F20" s="13">
+        <f>$B20/$G$9*$F$9</f>
         <v>180.24691358024694</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="13">
         <v>500</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="5">
-        <f>$B21/$E$6*$B$6</f>
+      <c r="D21" s="13">
+        <f>$B21/$G$6*$D$6</f>
         <v>100</v>
       </c>
-      <c r="E21" s="5">
-        <f>$B21/$E$6*$C$6</f>
+      <c r="E21" s="13">
+        <f>$B21/$G$6*$E$6</f>
         <v>150</v>
       </c>
-      <c r="F21" s="5">
-        <f>$B21/$E$6*$D$6</f>
+      <c r="F21" s="13">
+        <f>$B21/$G$6*$F$6</f>
         <v>250</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="13">
         <v>100</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="5">
-        <f>$B22/$E$6*$B$6</f>
+      <c r="D22" s="13">
+        <f>$B22/$G$6*$D$6</f>
         <v>20</v>
       </c>
-      <c r="E22" s="5">
-        <f>$B22/$E$6*$C$6</f>
+      <c r="E22" s="13">
+        <f>$B22/$G$6*$E$6</f>
         <v>30</v>
       </c>
-      <c r="F22" s="5">
-        <f>$B22/$E$6*$D$6</f>
+      <c r="F22" s="13">
+        <f>$B22/$G$6*$F$6</f>
         <v>50</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="13">
         <v>1250</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="5">
-        <f>$B23/$E$10*$B$10</f>
+      <c r="D23" s="13">
+        <f>$B23/$G$10*$D$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="E23" s="5">
-        <f>$B23/$E$10*$C$10</f>
+      <c r="E23" s="13">
+        <f>$B23/$G$10*$E$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="F23" s="5">
-        <f>$B23/$E$10*$D$10</f>
+      <c r="F23" s="13">
+        <f>$B23/$G$10*$F$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="G23" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
+      <c r="G23" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="14">
         <f>SUBTOTAL(109,B14:B23)</f>
         <v>9600</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16">
+      <c r="C24" s="19"/>
+      <c r="D24" s="14">
         <f>SUBTOTAL(109,D14:D23)</f>
         <v>2197.8121416131758</v>
       </c>
-      <c r="E24" s="16">
-        <f t="shared" ref="E24" si="4">SUBTOTAL(109,E14:E23)</f>
+      <c r="E24" s="14">
+        <f t="shared" ref="E24" si="1">SUBTOTAL(109,E14:E23)</f>
         <v>2876.2726770667587</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="14">
         <f>SUBTOTAL(109,F14:F23)</f>
         <v>4525.9151813200651</v>
       </c>
-      <c r="G24" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="G24" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="15">
         <f>SUM($D25:$F25)</f>
         <v>-9200</v>
       </c>
-      <c r="D25" s="7">
+      <c r="C25" s="20"/>
+      <c r="D25" s="15">
         <v>-2000</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="15">
         <v>-3000</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="15">
         <v>-4200</v>
       </c>
-      <c r="G25" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="G25" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="13">
         <f>SUM($D26:$F26)</f>
         <v>399.99999999999955</v>
       </c>
-      <c r="D26" s="9">
+      <c r="C26" s="21"/>
+      <c r="D26" s="13">
         <f>$D24+$D25</f>
         <v>197.81214161317575</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="13">
         <f>$E24+$E25</f>
         <v>-123.72732293324134</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="13">
         <f>$F24+$F25</f>
         <v>325.91518132006513</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="9">
         <v>10</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="13">
         <f>$F$24/12*10</f>
         <v>3771.5959844333879</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="13">
         <v>-3500</v>
       </c>
-      <c r="E29" s="12">
-        <f t="shared" ref="E29:E30" si="5">$C29+$D29</f>
+      <c r="E29" s="13">
+        <f t="shared" ref="E29:E30" si="2">$C29+$D29</f>
         <v>271.59598443338791</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="9">
         <v>2</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="13">
         <f>$F$24/12*2</f>
         <v>754.31919688667756</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="13">
         <v>-700</v>
       </c>
-      <c r="E30" s="12">
-        <f t="shared" si="5"/>
+      <c r="E30" s="13">
+        <f t="shared" si="2"/>
         <v>54.31919688667756</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+  </mergeCells>
   <conditionalFormatting sqref="D26:F26">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29:E30">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="3">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
+++ b/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\realestate\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B3EE1F-670D-4A15-8329-DB637D2C1EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E151A78-5BA4-46AD-B0BA-3DDA00C3C9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
   </bookViews>
@@ -141,13 +141,13 @@
     <t>Conguaglio</t>
   </si>
   <si>
-    <t>Differenze</t>
-  </si>
-  <si>
     <t>millesimi/centesimi</t>
   </si>
   <si>
     <t>millesimi</t>
+  </si>
+  <si>
+    <t>Controllo</t>
   </si>
 </sst>
 </file>
@@ -301,15 +301,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -358,11 +349,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -381,13 +388,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -775,499 +775,499 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="7" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="12">
+      <c r="A6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="9">
         <v>200</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="6">
         <v>300</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="6">
         <v>500</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="6">
         <f>SUM($D6:$F6)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="12">
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="9">
         <v>54</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>85</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6">
         <v>124</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="6">
         <f>SUM($D7:$F7)</f>
         <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="12">
+      <c r="B8" s="14"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="9">
         <v>10241</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>13400</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="6">
         <v>22578</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="6">
         <f>SUM($D8:$F8)</f>
         <v>46219</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="12">
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="9">
         <v>1104</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>1210</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="6">
         <v>1898</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="6">
         <f>SUM($D9:$F9)</f>
         <v>4212</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="12">
+      <c r="B10" s="14"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="9">
         <v>1</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>1</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="6">
         <v>1</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="6">
         <f>SUM($D10:$F10)</f>
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>34</v>
+      <c r="G13" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="10">
         <v>4000</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="10">
         <f>$B14/$G$8*$D$8</f>
         <v>886.30217010320439</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="10">
         <f>$B14/$G$8*$E$8</f>
         <v>1159.6962288236441</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="10">
         <f>$B14/$G$8*$F$8</f>
         <v>1954.0016010731517</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="10">
         <f>$B14-SUM($D14:$F14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="10">
         <v>2000</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="10">
         <f>$B15/$G$6*$D$6</f>
         <v>400</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="10">
         <f>$B15/$G$6*$E$6</f>
         <v>600</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="10">
         <f>$B15/$G$6*$F$6</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="10">
         <f t="shared" ref="G15:G26" si="0">$B15-SUM($D15:$F15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="10">
         <v>200</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="C16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="10">
         <f>$B16/$G$6*$D$6</f>
         <v>40</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="10">
         <f>$B16/$G$6*$E$6</f>
         <v>60</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="10">
         <f>$B16/$G$6*$F$6</f>
         <v>100</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="10">
         <v>50</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="13">
+      <c r="C17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="10">
         <f>$B17/$G$6*$D$6</f>
         <v>10</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="10">
         <f>$B17/$G$6*$E$6</f>
         <v>15</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="10">
         <f>$B17/$G$6*$F$6</f>
         <v>25</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="10">
         <v>800</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="13">
+      <c r="C18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="10">
         <f>$B18/$G$6*$D$6</f>
         <v>160</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="10">
         <f>$B18/$G$6*$E$6</f>
         <v>240</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="10">
         <f>$B18/$G$6*$F$6</f>
         <v>400</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="10">
         <v>300</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="13">
+      <c r="C19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="10">
         <f>$B19/$G$6*$D$6</f>
         <v>60</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="10">
         <f>$B19/$G$6*$E$6</f>
         <v>90</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="10">
         <f>$B19/$G$6*$F$6</f>
         <v>150</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="10">
         <v>400</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="10">
         <f>$B20/$G$9*$D$9</f>
         <v>104.84330484330485</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="10">
         <f>$B20/$G$9*$E$9</f>
         <v>114.90978157644825</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="10">
         <f>$B20/$G$9*$F$9</f>
         <v>180.24691358024694</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="10">
         <v>500</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="13">
+      <c r="C21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="10">
         <f>$B21/$G$6*$D$6</f>
         <v>100</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="10">
         <f>$B21/$G$6*$E$6</f>
         <v>150</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="10">
         <f>$B21/$G$6*$F$6</f>
         <v>250</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="10">
         <v>100</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="13">
+      <c r="C22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="10">
         <f>$B22/$G$6*$D$6</f>
         <v>20</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="10">
         <f>$B22/$G$6*$E$6</f>
         <v>30</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="10">
         <f>$B22/$G$6*$F$6</f>
         <v>50</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="10">
         <v>1250</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="10">
         <f>$B23/$G$10*$D$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="10">
         <f>$B23/$G$10*$E$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="10">
         <f>$B23/$G$10*$F$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="11">
         <f>SUBTOTAL(109,B14:B23)</f>
         <v>9600</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="14">
+      <c r="C24" s="16"/>
+      <c r="D24" s="11">
         <f>SUBTOTAL(109,D14:D23)</f>
         <v>2197.8121416131758</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="11">
         <f t="shared" ref="E24:F24" si="1">SUBTOTAL(109,E14:E23)</f>
         <v>2876.2726770667587</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="11">
         <f t="shared" si="1"/>
         <v>4525.9151813200651</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="12">
         <f>SUM($D25:$F25)</f>
         <v>-9200</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="15">
+      <c r="C25" s="17"/>
+      <c r="D25" s="12">
         <v>-2000</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="12">
         <v>-3000</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="12">
         <v>-4200</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="10">
         <f>SUM($D26:$F26)</f>
         <v>399.99999999999955</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="13">
+      <c r="C26" s="18"/>
+      <c r="D26" s="10">
         <f>$D24+$D25</f>
         <v>197.81214161317575</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="10">
         <f>$E24+$E25</f>
         <v>-123.72732293324134</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="10">
         <f>$F24+$F25</f>
         <v>325.91518132006513</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1327,554 +1327,554 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="7" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="9">
+      <c r="A6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="6">
         <v>200</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="6">
         <v>300</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="6">
         <v>500</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="6">
         <f>SUM($D6:$F6)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="9">
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="6">
         <v>54</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>85</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6">
         <v>124</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="6">
         <f>SUM($D7:$F7)</f>
         <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="9">
+      <c r="B8" s="14"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="6">
         <v>10241</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>13400</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="6">
         <v>22578</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="6">
         <f>SUM($D8:$F8)</f>
         <v>46219</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="9">
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="6">
         <v>1104</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>1210</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="6">
         <v>1898</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="6">
         <f>SUM($D9:$F9)</f>
         <v>4212</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="9">
+      <c r="B10" s="14"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="6">
         <v>1</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>1</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="6">
         <v>1</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="6">
         <f>SUM($D10:$F10)</f>
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>34</v>
+      <c r="G13" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="10">
         <v>4000</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="10">
         <f>$B14/$G$8*$D$8</f>
         <v>886.30217010320439</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="10">
         <f>$B14/$G$8*$E$8</f>
         <v>1159.6962288236441</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="10">
         <f>$B14/$G$8*$F$8</f>
         <v>1954.0016010731517</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="10">
         <f>$B14-SUM($D14:$F14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="10">
         <v>2000</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="10">
         <f>$B15/$G$6*$D$6</f>
         <v>400</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="10">
         <f>$B15/$G$6*$E$6</f>
         <v>600</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="10">
         <f>$B15/$G$6*$F$6</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="10">
         <f t="shared" ref="G15:G26" si="0">$B15-SUM($D15:$F15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="10">
         <v>200</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="C16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="10">
         <f>$B16/$G$6*$D$6</f>
         <v>40</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="10">
         <f>$B16/$G$6*$E$6</f>
         <v>60</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="10">
         <f>$B16/$G$6*$F$6</f>
         <v>100</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="10">
         <v>50</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="13">
+      <c r="C17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="10">
         <f>$B17/$G$6*$D$6</f>
         <v>10</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="10">
         <f>$B17/$G$6*$E$6</f>
         <v>15</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="10">
         <f>$B17/$G$6*$F$6</f>
         <v>25</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="10">
         <v>800</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="13">
+      <c r="C18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="10">
         <f>$B18/$G$6*$D$6</f>
         <v>160</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="10">
         <f>$B18/$G$6*$E$6</f>
         <v>240</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="10">
         <f>$B18/$G$6*$F$6</f>
         <v>400</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="10">
         <v>300</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="13">
+      <c r="C19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="10">
         <f>$B19/$G$6*$D$6</f>
         <v>60</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="10">
         <f>$B19/$G$6*$E$6</f>
         <v>90</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="10">
         <f>$B19/$G$6*$F$6</f>
         <v>150</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="10">
         <v>400</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="10">
         <f>$B20/$G$9*$D$9</f>
         <v>104.84330484330485</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="10">
         <f>$B20/$G$9*$E$9</f>
         <v>114.90978157644825</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="10">
         <f>$B20/$G$9*$F$9</f>
         <v>180.24691358024694</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="10">
         <v>500</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="13">
+      <c r="C21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="10">
         <f>$B21/$G$6*$D$6</f>
         <v>100</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="10">
         <f>$B21/$G$6*$E$6</f>
         <v>150</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="10">
         <f>$B21/$G$6*$F$6</f>
         <v>250</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="10">
         <v>100</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="13">
+      <c r="C22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="10">
         <f>$B22/$G$6*$D$6</f>
         <v>20</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="10">
         <f>$B22/$G$6*$E$6</f>
         <v>30</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="10">
         <f>$B22/$G$6*$F$6</f>
         <v>50</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="10">
         <v>1250</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="10">
         <f>$B23/$G$10*$D$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="10">
         <f>$B23/$G$10*$E$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="10">
         <f>$B23/$G$10*$F$10</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="11">
         <f>SUBTOTAL(109,B14:B23)</f>
         <v>9600</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="14">
+      <c r="C24" s="16"/>
+      <c r="D24" s="11">
         <f>SUBTOTAL(109,D14:D23)</f>
         <v>2197.8121416131758</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="11">
         <f t="shared" ref="E24" si="1">SUBTOTAL(109,E14:E23)</f>
         <v>2876.2726770667587</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="11">
         <f>SUBTOTAL(109,F14:F23)</f>
         <v>4525.9151813200651</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="12">
         <f>SUM($D25:$F25)</f>
         <v>-9200</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="15">
+      <c r="C25" s="17"/>
+      <c r="D25" s="12">
         <v>-2000</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="12">
         <v>-3000</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="12">
         <v>-4200</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="10">
         <f>SUM($D26:$F26)</f>
         <v>399.99999999999955</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="13">
+      <c r="C26" s="18"/>
+      <c r="D26" s="10">
         <f>$D24+$D25</f>
         <v>197.81214161317575</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="10">
         <f>$E24+$E25</f>
         <v>-123.72732293324134</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="10">
         <f>$F24+$F25</f>
         <v>325.91518132006513</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="6">
         <v>10</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="10">
         <f>$F$24/12*10</f>
         <v>3771.5959844333879</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="10">
         <v>-3500</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="10">
         <f t="shared" ref="E29:E30" si="2">$C29+$D29</f>
         <v>271.59598443338791</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="6">
         <v>2</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="10">
         <f>$F$24/12*2</f>
         <v>754.31919688667756</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="10">
         <v>-700</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="10">
         <f t="shared" si="2"/>
         <v>54.31919688667756</v>
       </c>
@@ -1891,18 +1891,18 @@
     <mergeCell ref="A10:C10"/>
   </mergeCells>
   <conditionalFormatting sqref="D26:F26">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29:E30">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
+++ b/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\realestate\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E151A78-5BA4-46AD-B0BA-3DDA00C3C9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5FFC63-DD99-4F19-B100-E0A5497CD082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
   </bookViews>
   <sheets>
     <sheet name="Conguagli spese" sheetId="4" r:id="rId1"/>

--- a/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
+++ b/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\realestate\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5FFC63-DD99-4F19-B100-E0A5497CD082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C8C881-1E1C-47EE-ACE8-7946ECC8FCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
   </bookViews>
   <sheets>
     <sheet name="Conguagli spese" sheetId="4" r:id="rId1"/>
@@ -196,7 +196,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -280,24 +280,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -344,9 +331,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -775,11 +759,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="21"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
@@ -1254,7 +1238,7 @@
         <f>SUM($D26:$F26)</f>
         <v>399.99999999999955</v>
       </c>
-      <c r="C26" s="18"/>
+      <c r="C26" s="17"/>
       <c r="D26" s="10">
         <f>$D24+$D25</f>
         <v>197.81214161317575</v>
@@ -1327,11 +1311,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="21"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
@@ -1806,7 +1790,7 @@
         <f>SUM($D26:$F26)</f>
         <v>399.99999999999955</v>
       </c>
-      <c r="C26" s="18"/>
+      <c r="C26" s="17"/>
       <c r="D26" s="10">
         <f>$D24+$D25</f>
         <v>197.81214161317575</v>

--- a/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
+++ b/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\realestate\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C8C881-1E1C-47EE-ACE8-7946ECC8FCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FF7200-F039-40C8-9091-DCCA1A1E157C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="44">
   <si>
     <t>Riscaldamento</t>
   </si>
@@ -148,6 +148,27 @@
   </si>
   <si>
     <t>Controllo</t>
+  </si>
+  <si>
+    <t>App. 4</t>
+  </si>
+  <si>
+    <t>App. 5</t>
+  </si>
+  <si>
+    <t>App. 6</t>
+  </si>
+  <si>
+    <t>App. 7</t>
+  </si>
+  <si>
+    <t>App. 8</t>
+  </si>
+  <si>
+    <t>App. 9</t>
+  </si>
+  <si>
+    <t>App. 10</t>
   </si>
 </sst>
 </file>
@@ -284,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -342,11 +363,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -730,24 +774,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9073075C-C130-45EE-B2DF-A3C8E1CA77C7}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" customWidth="1"/>
     <col min="2" max="3" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -758,7 +802,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>22</v>
       </c>
@@ -774,30 +818,72 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="15"/>
       <c r="D6" s="9">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="E6" s="6">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="F6" s="6">
-        <v>500</v>
-      </c>
-      <c r="G6" s="6">
-        <f>SUM($D6:$F6)</f>
+        <v>125</v>
+      </c>
+      <c r="G6" s="9">
+        <v>70</v>
+      </c>
+      <c r="H6" s="6">
+        <v>80</v>
+      </c>
+      <c r="I6" s="6">
+        <v>125</v>
+      </c>
+      <c r="J6" s="6">
+        <v>140</v>
+      </c>
+      <c r="K6" s="9">
+        <v>85</v>
+      </c>
+      <c r="L6" s="6">
+        <v>85</v>
+      </c>
+      <c r="M6" s="6">
+        <v>140</v>
+      </c>
+      <c r="N6" s="6">
+        <f>SUM($D6:$M6)</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>16</v>
       </c>
@@ -812,12 +898,33 @@
       <c r="F7" s="6">
         <v>124</v>
       </c>
-      <c r="G7" s="6">
-        <f>SUM($D7:$F7)</f>
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7" s="9">
+        <v>54</v>
+      </c>
+      <c r="H7" s="6">
+        <v>85</v>
+      </c>
+      <c r="I7" s="6">
+        <v>124</v>
+      </c>
+      <c r="J7" s="6">
+        <v>130</v>
+      </c>
+      <c r="K7" s="9">
+        <v>95</v>
+      </c>
+      <c r="L7" s="6">
+        <v>95</v>
+      </c>
+      <c r="M7" s="6">
+        <v>130</v>
+      </c>
+      <c r="N7" s="6">
+        <f>SUM($D7:$M7)</f>
+        <v>976</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>25</v>
       </c>
@@ -832,12 +939,33 @@
       <c r="F8" s="6">
         <v>22578</v>
       </c>
-      <c r="G8" s="6">
-        <f>SUM($D8:$F8)</f>
-        <v>46219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G8" s="9">
+        <v>9980</v>
+      </c>
+      <c r="H8" s="6">
+        <v>15050</v>
+      </c>
+      <c r="I8" s="6">
+        <v>20200</v>
+      </c>
+      <c r="J8" s="6">
+        <v>21000</v>
+      </c>
+      <c r="K8" s="9">
+        <v>8690</v>
+      </c>
+      <c r="L8" s="6">
+        <v>10900</v>
+      </c>
+      <c r="M8" s="6">
+        <v>19000</v>
+      </c>
+      <c r="N8" s="6">
+        <f>SUM($D8:$M8)</f>
+        <v>151039</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
@@ -852,12 +980,33 @@
       <c r="F9" s="6">
         <v>1898</v>
       </c>
-      <c r="G9" s="6">
-        <f>SUM($D9:$F9)</f>
-        <v>4212</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G9" s="9">
+        <v>902</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1050</v>
+      </c>
+      <c r="I9" s="6">
+        <v>1490</v>
+      </c>
+      <c r="J9" s="6">
+        <v>1520</v>
+      </c>
+      <c r="K9" s="9">
+        <v>1385</v>
+      </c>
+      <c r="L9" s="6">
+        <v>1140</v>
+      </c>
+      <c r="M9" s="6">
+        <v>1925</v>
+      </c>
+      <c r="N9" s="6">
+        <f>SUM($D9:$M9)</f>
+        <v>13624</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>17</v>
       </c>
@@ -872,12 +1021,33 @@
       <c r="F10" s="6">
         <v>1</v>
       </c>
-      <c r="G10" s="6">
-        <f>SUM($D10:$F10)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G10" s="9">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1</v>
+      </c>
+      <c r="J10" s="6">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6">
+        <v>1</v>
+      </c>
+      <c r="M10" s="6">
+        <v>1</v>
+      </c>
+      <c r="N10" s="6">
+        <f>SUM($D10:$M10)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>24</v>
       </c>
@@ -886,9 +1056,16 @@
       <c r="D11" s="9"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G11" s="9"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -908,312 +1085,641 @@
         <v>15</v>
       </c>
       <c r="G13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="10">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="10">
-        <f>$B14/$G$8*$D$8</f>
-        <v>886.30217010320439</v>
+        <f>$B14/$N$8*$D$8</f>
+        <v>678.03679844278622</v>
       </c>
       <c r="E14" s="10">
-        <f>$B14/$G$8*$E$8</f>
-        <v>1159.6962288236441</v>
+        <f>$B14/$N$8*$E$8</f>
+        <v>887.18807725157069</v>
       </c>
       <c r="F14" s="10">
-        <f>$B14/$G$8*$F$8</f>
-        <v>1954.0016010731517</v>
+        <f>$B14/$N$8*$F$8</f>
+        <v>1494.8457021034301</v>
       </c>
       <c r="G14" s="10">
-        <f>$B14-SUM($D14:$F14)</f>
+        <f>$B14/$N$8*$G$8</f>
+        <v>660.75649335602054</v>
+      </c>
+      <c r="H14" s="10">
+        <f>$B14/$N$8*$H$8</f>
+        <v>996.43138527135363</v>
+      </c>
+      <c r="I14" s="10">
+        <f>$B14/$N$8*$I$8</f>
+        <v>1337.4029224240096</v>
+      </c>
+      <c r="J14" s="10">
+        <f>$B14/$N$8*$J$8</f>
+        <v>1390.3693747972377</v>
+      </c>
+      <c r="K14" s="10">
+        <f>$B14/$N$8*$K$8</f>
+        <v>575.34808890419026</v>
+      </c>
+      <c r="L14" s="10">
+        <f>$B14/$N$8*$L$8</f>
+        <v>721.6679135852329</v>
+      </c>
+      <c r="M14" s="10">
+        <f>$B14/$N$8*$M$8</f>
+        <v>1257.9532438641675</v>
+      </c>
+      <c r="N14" s="10">
+        <f>$B14-SUM($D14:$M14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B15" s="10">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="10">
-        <f>$B15/$G$6*$D$6</f>
-        <v>400</v>
+        <f>$B15/$N$6*$D$6</f>
+        <v>420</v>
       </c>
       <c r="E15" s="10">
-        <f>$B15/$G$6*$E$6</f>
-        <v>600</v>
+        <f>$B15/$N$6*$E$6</f>
+        <v>480</v>
       </c>
       <c r="F15" s="10">
-        <f>$B15/$G$6*$F$6</f>
-        <v>1000</v>
+        <f>$B15/$N$6*$F$6</f>
+        <v>750</v>
       </c>
       <c r="G15" s="10">
-        <f t="shared" ref="G15:G26" si="0">$B15-SUM($D15:$F15)</f>
+        <f>$B15/$N$6*$G$6</f>
+        <v>420</v>
+      </c>
+      <c r="H15" s="10">
+        <f>$B15/$N$6*$H$6</f>
+        <v>480</v>
+      </c>
+      <c r="I15" s="10">
+        <f>$B15/$N$6*$I$6</f>
+        <v>750</v>
+      </c>
+      <c r="J15" s="10">
+        <f>$B15/$N$6*$J$6</f>
+        <v>840</v>
+      </c>
+      <c r="K15" s="10">
+        <f>$B15/$N$6*$K$6</f>
+        <v>510</v>
+      </c>
+      <c r="L15" s="10">
+        <f>$B15/$N$6*$L$6</f>
+        <v>510</v>
+      </c>
+      <c r="M15" s="10">
+        <f>$B15/$N$6*$M$6</f>
+        <v>840</v>
+      </c>
+      <c r="N15" s="10">
+        <f>$B15-SUM($D15:$M15)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B16" s="10">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D16" s="10">
-        <f>$B16/$G$6*$D$6</f>
-        <v>40</v>
+        <f>$B16/$N$6*$D$6</f>
+        <v>42</v>
       </c>
       <c r="E16" s="10">
-        <f>$B16/$G$6*$E$6</f>
-        <v>60</v>
+        <f>$B16/$N$6*$E$6</f>
+        <v>48</v>
       </c>
       <c r="F16" s="10">
-        <f>$B16/$G$6*$F$6</f>
-        <v>100</v>
+        <f>$B16/$N$6*$F$6</f>
+        <v>75</v>
       </c>
       <c r="G16" s="10">
+        <f>$B16/$N$6*$G$6</f>
+        <v>42</v>
+      </c>
+      <c r="H16" s="10">
+        <f>$B16/$N$6*$H$6</f>
+        <v>48</v>
+      </c>
+      <c r="I16" s="10">
+        <f>$B16/$N$6*$I$6</f>
+        <v>75</v>
+      </c>
+      <c r="J16" s="10">
+        <f>$B16/$N$6*$J$6</f>
+        <v>84</v>
+      </c>
+      <c r="K16" s="10">
+        <f>$B16/$N$6*$K$6</f>
+        <v>51</v>
+      </c>
+      <c r="L16" s="10">
+        <f>$B16/$N$6*$L$6</f>
+        <v>51</v>
+      </c>
+      <c r="M16" s="10">
+        <f>$B16/$N$6*$M$6</f>
+        <v>84</v>
+      </c>
+      <c r="N16" s="10">
+        <f t="shared" ref="N16:N23" si="0">$B16-SUM($D16:$M16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="10">
+        <v>150</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="10">
+        <f>$B17/$N$6*$D$6</f>
+        <v>10.5</v>
+      </c>
+      <c r="E17" s="10">
+        <f>$B17/$N$6*$E$6</f>
+        <v>12</v>
+      </c>
+      <c r="F17" s="10">
+        <f>$B17/$N$6*$F$6</f>
+        <v>18.75</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" ref="G17:G19" si="1">$B17/$N$6*$G$6</f>
+        <v>10.5</v>
+      </c>
+      <c r="H17" s="10">
+        <f t="shared" ref="H17:H19" si="2">$B17/$N$6*$H$6</f>
+        <v>12</v>
+      </c>
+      <c r="I17" s="10">
+        <f>$B17/$N$6*$I$6</f>
+        <v>18.75</v>
+      </c>
+      <c r="J17" s="10">
+        <f>$B17/$N$6*$J$6</f>
+        <v>21</v>
+      </c>
+      <c r="K17" s="10">
+        <f>$B17/$N$6*$K$6</f>
+        <v>12.75</v>
+      </c>
+      <c r="L17" s="10">
+        <f>$B17/$N$6*$L$6</f>
+        <v>12.75</v>
+      </c>
+      <c r="M17" s="10">
+        <f>$B17/$N$6*$M$6</f>
+        <v>21</v>
+      </c>
+      <c r="N17" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="10">
-        <v>50</v>
-      </c>
-      <c r="C17" s="5" t="s">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="10">
+        <v>2400</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="10">
-        <f>$B17/$G$6*$D$6</f>
-        <v>10</v>
-      </c>
-      <c r="E17" s="10">
-        <f>$B17/$G$6*$E$6</f>
-        <v>15</v>
-      </c>
-      <c r="F17" s="10">
-        <f>$B17/$G$6*$F$6</f>
-        <v>25</v>
-      </c>
-      <c r="G17" s="10">
+      <c r="D18" s="10">
+        <f>$B18/$N$6*$D$6</f>
+        <v>168</v>
+      </c>
+      <c r="E18" s="10">
+        <f>$B18/$N$6*$E$6</f>
+        <v>192</v>
+      </c>
+      <c r="F18" s="10">
+        <f>$B18/$N$6*$F$6</f>
+        <v>300</v>
+      </c>
+      <c r="G18" s="10">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+      <c r="H18" s="10">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+      <c r="I18" s="10">
+        <f>$B18/$N$6*$I$6</f>
+        <v>300</v>
+      </c>
+      <c r="J18" s="10">
+        <f>$B18/$N$6*$J$6</f>
+        <v>336</v>
+      </c>
+      <c r="K18" s="10">
+        <f>$B18/$N$6*$K$6</f>
+        <v>204</v>
+      </c>
+      <c r="L18" s="10">
+        <f>$B18/$N$6*$L$6</f>
+        <v>204</v>
+      </c>
+      <c r="M18" s="10">
+        <f>$B18/$N$6*$M$6</f>
+        <v>336</v>
+      </c>
+      <c r="N18" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="10">
-        <v>800</v>
-      </c>
-      <c r="C18" s="5" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="10">
+        <v>900</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="10">
-        <f>$B18/$G$6*$D$6</f>
-        <v>160</v>
-      </c>
-      <c r="E18" s="10">
-        <f>$B18/$G$6*$E$6</f>
-        <v>240</v>
-      </c>
-      <c r="F18" s="10">
-        <f>$B18/$G$6*$F$6</f>
-        <v>400</v>
-      </c>
-      <c r="G18" s="10">
+      <c r="D19" s="10">
+        <f>$B19/$N$6*$D$6</f>
+        <v>63</v>
+      </c>
+      <c r="E19" s="10">
+        <f>$B19/$N$6*$E$6</f>
+        <v>72</v>
+      </c>
+      <c r="F19" s="10">
+        <f>$B19/$N$6*$F$6</f>
+        <v>112.5</v>
+      </c>
+      <c r="G19" s="10">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="H19" s="10">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="I19" s="10">
+        <f>$B19/$N$6*$I$6</f>
+        <v>112.5</v>
+      </c>
+      <c r="J19" s="10">
+        <f>$B19/$N$6*$J$6</f>
+        <v>126</v>
+      </c>
+      <c r="K19" s="10">
+        <f>$B19/$N$6*$K$6</f>
+        <v>76.5</v>
+      </c>
+      <c r="L19" s="10">
+        <f>$B19/$N$6*$L$6</f>
+        <v>76.5</v>
+      </c>
+      <c r="M19" s="10">
+        <f>$B19/$N$6*$M$6</f>
+        <v>126</v>
+      </c>
+      <c r="N19" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="10">
-        <v>300</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="10">
-        <f>$B19/$G$6*$D$6</f>
-        <v>60</v>
-      </c>
-      <c r="E19" s="10">
-        <f>$B19/$G$6*$E$6</f>
-        <v>90</v>
-      </c>
-      <c r="F19" s="10">
-        <f>$B19/$G$6*$F$6</f>
-        <v>150</v>
-      </c>
-      <c r="G19" s="10">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="10">
+        <v>1200</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="10">
+        <f>$B20/$N$9*$D$9</f>
+        <v>97.240164415736942</v>
+      </c>
+      <c r="E20" s="10">
+        <f>$B20/$N$9*$E$9</f>
+        <v>106.57662947739284</v>
+      </c>
+      <c r="F20" s="10">
+        <f>$B20/$N$9*$F$9</f>
+        <v>167.17557251908397</v>
+      </c>
+      <c r="G20" s="10">
+        <f>$B20/$N$9*$G$9</f>
+        <v>79.448032883147391</v>
+      </c>
+      <c r="H20" s="10">
+        <f>$B20/$N$9*$H$9</f>
+        <v>92.483852025836754</v>
+      </c>
+      <c r="I20" s="10">
+        <f>$B20/$N$9*$I$9</f>
+        <v>131.23899001761598</v>
+      </c>
+      <c r="J20" s="10">
+        <f>$B20/$N$9*$J$9</f>
+        <v>133.88138578978274</v>
+      </c>
+      <c r="K20" s="10">
+        <f>$B20/$N$9*$K$9</f>
+        <v>121.9906048150323</v>
+      </c>
+      <c r="L20" s="10">
+        <f>$B20/$N$9*$L$9</f>
+        <v>100.41103934233705</v>
+      </c>
+      <c r="M20" s="10">
+        <f>$B20/$N$9*$M$9</f>
+        <v>169.55372871403407</v>
+      </c>
+      <c r="N20" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="10">
-        <v>400</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="10">
-        <f>$B20/$G$9*$D$9</f>
-        <v>104.84330484330485</v>
-      </c>
-      <c r="E20" s="10">
-        <f>$B20/$G$9*$E$9</f>
-        <v>114.90978157644825</v>
-      </c>
-      <c r="F20" s="10">
-        <f>$B20/$G$9*$F$9</f>
-        <v>180.24691358024694</v>
-      </c>
-      <c r="G20" s="10">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="10">
+        <v>1500</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="10">
+        <f>$B21/$N$6*$D$6</f>
+        <v>105</v>
+      </c>
+      <c r="E21" s="10">
+        <f>$B21/$N$6*$E$6</f>
+        <v>120</v>
+      </c>
+      <c r="F21" s="10">
+        <f>$B21/$N$6*$F$6</f>
+        <v>187.5</v>
+      </c>
+      <c r="G21" s="10">
+        <f>$B21/$N$6*$G$6</f>
+        <v>105</v>
+      </c>
+      <c r="H21" s="10">
+        <f>$B21/$N$6*$H$6</f>
+        <v>120</v>
+      </c>
+      <c r="I21" s="10">
+        <f>$B21/$N$6*$I$6</f>
+        <v>187.5</v>
+      </c>
+      <c r="J21" s="10">
+        <f>$B21/$N$6*$J$6</f>
+        <v>210</v>
+      </c>
+      <c r="K21" s="10">
+        <f>$B21/$N$6*$K$6</f>
+        <v>127.5</v>
+      </c>
+      <c r="L21" s="10">
+        <f>$B21/$N$6*$L$6</f>
+        <v>127.5</v>
+      </c>
+      <c r="M21" s="10">
+        <f>$B21/$N$6*$M$6</f>
+        <v>210</v>
+      </c>
+      <c r="N21" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="10">
-        <v>500</v>
-      </c>
-      <c r="C21" s="5" t="s">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="10">
+        <v>190</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="10">
-        <f>$B21/$G$6*$D$6</f>
-        <v>100</v>
-      </c>
-      <c r="E21" s="10">
-        <f>$B21/$G$6*$E$6</f>
-        <v>150</v>
-      </c>
-      <c r="F21" s="10">
-        <f>$B21/$G$6*$F$6</f>
-        <v>250</v>
-      </c>
-      <c r="G21" s="10">
+      <c r="D22" s="10">
+        <f>$B22/$N$6*$D$6</f>
+        <v>13.3</v>
+      </c>
+      <c r="E22" s="10">
+        <f>$B22/$N$6*$E$6</f>
+        <v>15.2</v>
+      </c>
+      <c r="F22" s="10">
+        <f>$B22/$N$6*$F$6</f>
+        <v>23.75</v>
+      </c>
+      <c r="G22" s="10">
+        <f>$B22/$N$6*$G$6</f>
+        <v>13.3</v>
+      </c>
+      <c r="H22" s="10">
+        <f>$B22/$N$6*$H$6</f>
+        <v>15.2</v>
+      </c>
+      <c r="I22" s="10">
+        <f>$B22/$N$6*$I$6</f>
+        <v>23.75</v>
+      </c>
+      <c r="J22" s="10">
+        <f>$B22/$N$6*$J$6</f>
+        <v>26.6</v>
+      </c>
+      <c r="K22" s="10">
+        <f>$B22/$N$6*$K$6</f>
+        <v>16.149999999999999</v>
+      </c>
+      <c r="L22" s="10">
+        <f>$B22/$N$6*$L$6</f>
+        <v>16.149999999999999</v>
+      </c>
+      <c r="M22" s="10">
+        <f>$B22/$N$6*$M$6</f>
+        <v>26.6</v>
+      </c>
+      <c r="N22" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="10">
-        <v>100</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="10">
-        <f>$B22/$G$6*$D$6</f>
-        <v>20</v>
-      </c>
-      <c r="E22" s="10">
-        <f>$B22/$G$6*$E$6</f>
-        <v>30</v>
-      </c>
-      <c r="F22" s="10">
-        <f>$B22/$G$6*$F$6</f>
-        <v>50</v>
-      </c>
-      <c r="G22" s="10">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="10">
+        <v>3750</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="10">
+        <f>$B23/$N$10*$D$10</f>
+        <v>375</v>
+      </c>
+      <c r="E23" s="10">
+        <f>$B23/$N$10*$E$10</f>
+        <v>375</v>
+      </c>
+      <c r="F23" s="10">
+        <f>$B23/$N$10*$F$10</f>
+        <v>375</v>
+      </c>
+      <c r="G23" s="10">
+        <f>$B23/$N$10*$G$10</f>
+        <v>375</v>
+      </c>
+      <c r="H23" s="10">
+        <f>$B23/$N$10*$H$10</f>
+        <v>375</v>
+      </c>
+      <c r="I23" s="10">
+        <f>$B23/$N$10*$I$10</f>
+        <v>375</v>
+      </c>
+      <c r="J23" s="10">
+        <f>$B23/$N$10*$J$10</f>
+        <v>375</v>
+      </c>
+      <c r="K23" s="10">
+        <f>$B23/$N$10*$K$10</f>
+        <v>375</v>
+      </c>
+      <c r="L23" s="10">
+        <f>$B23/$N$10*$L$10</f>
+        <v>375</v>
+      </c>
+      <c r="M23" s="10">
+        <f>$B23/$N$10*$M$10</f>
+        <v>375</v>
+      </c>
+      <c r="N23" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="10">
-        <v>1250</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="10">
-        <f>$B23/$G$10*$D$10</f>
-        <v>416.66666666666669</v>
-      </c>
-      <c r="E23" s="10">
-        <f>$B23/$G$10*$E$10</f>
-        <v>416.66666666666669</v>
-      </c>
-      <c r="F23" s="10">
-        <f>$B23/$G$10*$F$10</f>
-        <v>416.66666666666669</v>
-      </c>
-      <c r="G23" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B24" s="11">
         <f>SUBTOTAL(109,B14:B23)</f>
-        <v>9600</v>
+        <v>26690</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="11">
         <f>SUBTOTAL(109,D14:D23)</f>
-        <v>2197.8121416131758</v>
+        <v>1972.0769628585231</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" ref="E24:F24" si="1">SUBTOTAL(109,E14:E23)</f>
-        <v>2876.2726770667587</v>
+        <f t="shared" ref="E24:F24" si="3">SUBTOTAL(109,E14:E23)</f>
+        <v>2307.9647067289634</v>
       </c>
       <c r="F24" s="11">
-        <f t="shared" si="1"/>
-        <v>4525.9151813200651</v>
+        <f t="shared" si="3"/>
+        <v>3504.5212746225143</v>
       </c>
       <c r="G24" s="11">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(109,G14:G23)</f>
+        <v>1937.0045262391679</v>
+      </c>
+      <c r="H24" s="11">
+        <f t="shared" ref="H24:J24" si="4">SUBTOTAL(109,H14:H23)</f>
+        <v>2403.1152372971901</v>
+      </c>
+      <c r="I24" s="11">
+        <f t="shared" si="4"/>
+        <v>3311.1419124416252</v>
+      </c>
+      <c r="J24" s="11">
+        <f t="shared" si="4"/>
+        <v>3542.85076058702</v>
+      </c>
+      <c r="K24" s="11">
+        <f>SUBTOTAL(109,K14:K23)</f>
+        <v>2070.2386937192227</v>
+      </c>
+      <c r="L24" s="11">
+        <f t="shared" ref="L24:M24" si="5">SUBTOTAL(109,L14:L23)</f>
+        <v>2194.9789529275699</v>
+      </c>
+      <c r="M24" s="11">
+        <f t="shared" si="5"/>
+        <v>3446.1069725782013</v>
+      </c>
+      <c r="N24" s="21">
+        <f>$B24-SUM($D24:$M24)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B25" s="12">
-        <f>SUM($D25:$F25)</f>
-        <v>-9200</v>
+        <f>SUM($D25:$M25)</f>
+        <v>-31800</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="12">
@@ -1226,33 +1732,82 @@
         <v>-4200</v>
       </c>
       <c r="G25" s="12">
-        <f t="shared" si="0"/>
+        <v>-2000</v>
+      </c>
+      <c r="H25" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="I25" s="12">
+        <v>-4200</v>
+      </c>
+      <c r="J25" s="12">
+        <v>-4200</v>
+      </c>
+      <c r="K25" s="12">
+        <v>-2000</v>
+      </c>
+      <c r="L25" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="M25" s="12">
+        <v>-4200</v>
+      </c>
+      <c r="N25" s="12">
+        <f>$B25-SUM($D25:$M25)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B26" s="10">
-        <f>SUM($D26:$F26)</f>
-        <v>399.99999999999955</v>
+        <f>SUM($D26:$M26)</f>
+        <v>-5110.0000000000018</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="10">
         <f>$D24+$D25</f>
-        <v>197.81214161317575</v>
+        <v>-27.923037141476925</v>
       </c>
       <c r="E26" s="10">
         <f>$E24+$E25</f>
-        <v>-123.72732293324134</v>
+        <v>-692.03529327103661</v>
       </c>
       <c r="F26" s="10">
         <f>$F24+$F25</f>
-        <v>325.91518132006513</v>
+        <v>-695.47872537748572</v>
       </c>
       <c r="G26" s="10">
-        <f t="shared" si="0"/>
+        <f>$G24+$G25</f>
+        <v>-62.995473760832056</v>
+      </c>
+      <c r="H26" s="10">
+        <f>$H24+$H25</f>
+        <v>-596.88476270280989</v>
+      </c>
+      <c r="I26" s="10">
+        <f>$I24+$I25</f>
+        <v>-888.85808755837479</v>
+      </c>
+      <c r="J26" s="10">
+        <f>$J24+$J25</f>
+        <v>-657.14923941298002</v>
+      </c>
+      <c r="K26" s="10">
+        <f>$K24+$K25</f>
+        <v>70.238693719222738</v>
+      </c>
+      <c r="L26" s="10">
+        <f>$L24+$L25</f>
+        <v>-805.02104707243006</v>
+      </c>
+      <c r="M26" s="10">
+        <f>$M24+$M25</f>
+        <v>-753.89302742179871</v>
+      </c>
+      <c r="N26" s="10">
+        <f>$B26-SUM($D26:$M26)</f>
         <v>0</v>
       </c>
     </row>
@@ -1267,21 +1822,22 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A10:C10"/>
   </mergeCells>
-  <conditionalFormatting sqref="D26:F26">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="D26:M26">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEEC9161-9944-4F33-924D-68E41F754380}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.33203125" customWidth="1"/>
@@ -1289,17 +1845,17 @@
     <col min="5" max="5" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1310,7 +1866,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>22</v>
       </c>
@@ -1326,36 +1882,78 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="15"/>
-      <c r="D6" s="6">
-        <v>200</v>
+      <c r="D6" s="9">
+        <v>70</v>
       </c>
       <c r="E6" s="6">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="F6" s="6">
-        <v>500</v>
-      </c>
-      <c r="G6" s="6">
-        <f>SUM($D6:$F6)</f>
+        <v>125</v>
+      </c>
+      <c r="G6" s="9">
+        <v>70</v>
+      </c>
+      <c r="H6" s="6">
+        <v>80</v>
+      </c>
+      <c r="I6" s="6">
+        <v>125</v>
+      </c>
+      <c r="J6" s="6">
+        <v>140</v>
+      </c>
+      <c r="K6" s="9">
+        <v>85</v>
+      </c>
+      <c r="L6" s="6">
+        <v>85</v>
+      </c>
+      <c r="M6" s="6">
+        <v>140</v>
+      </c>
+      <c r="N6" s="6">
+        <f>SUM($D6:$M6)</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="15"/>
-      <c r="D7" s="6">
+      <c r="D7" s="9">
         <v>54</v>
       </c>
       <c r="E7" s="6">
@@ -1364,18 +1962,39 @@
       <c r="F7" s="6">
         <v>124</v>
       </c>
-      <c r="G7" s="6">
-        <f>SUM($D7:$F7)</f>
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7" s="9">
+        <v>54</v>
+      </c>
+      <c r="H7" s="6">
+        <v>85</v>
+      </c>
+      <c r="I7" s="6">
+        <v>124</v>
+      </c>
+      <c r="J7" s="6">
+        <v>130</v>
+      </c>
+      <c r="K7" s="9">
+        <v>95</v>
+      </c>
+      <c r="L7" s="6">
+        <v>95</v>
+      </c>
+      <c r="M7" s="6">
+        <v>130</v>
+      </c>
+      <c r="N7" s="6">
+        <f>SUM($D7:$M7)</f>
+        <v>976</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>25</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="15"/>
-      <c r="D8" s="6">
+      <c r="D8" s="9">
         <v>10241</v>
       </c>
       <c r="E8" s="6">
@@ -1384,18 +2003,39 @@
       <c r="F8" s="6">
         <v>22578</v>
       </c>
-      <c r="G8" s="6">
-        <f>SUM($D8:$F8)</f>
-        <v>46219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G8" s="9">
+        <v>9980</v>
+      </c>
+      <c r="H8" s="6">
+        <v>15050</v>
+      </c>
+      <c r="I8" s="6">
+        <v>20200</v>
+      </c>
+      <c r="J8" s="6">
+        <v>21000</v>
+      </c>
+      <c r="K8" s="9">
+        <v>8690</v>
+      </c>
+      <c r="L8" s="6">
+        <v>10900</v>
+      </c>
+      <c r="M8" s="6">
+        <v>19000</v>
+      </c>
+      <c r="N8" s="6">
+        <f>SUM($D8:$M8)</f>
+        <v>151039</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="15"/>
-      <c r="D9" s="6">
+      <c r="D9" s="9">
         <v>1104</v>
       </c>
       <c r="E9" s="6">
@@ -1404,18 +2044,39 @@
       <c r="F9" s="6">
         <v>1898</v>
       </c>
-      <c r="G9" s="6">
-        <f>SUM($D9:$F9)</f>
-        <v>4212</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G9" s="9">
+        <v>902</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1050</v>
+      </c>
+      <c r="I9" s="6">
+        <v>1490</v>
+      </c>
+      <c r="J9" s="6">
+        <v>1520</v>
+      </c>
+      <c r="K9" s="9">
+        <v>1385</v>
+      </c>
+      <c r="L9" s="6">
+        <v>1140</v>
+      </c>
+      <c r="M9" s="6">
+        <v>1925</v>
+      </c>
+      <c r="N9" s="6">
+        <f>SUM($D9:$M9)</f>
+        <v>13624</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="15"/>
-      <c r="D10" s="6">
+      <c r="D10" s="9">
         <v>1</v>
       </c>
       <c r="E10" s="6">
@@ -1424,23 +2085,51 @@
       <c r="F10" s="6">
         <v>1</v>
       </c>
-      <c r="G10" s="6">
-        <f>SUM($D10:$F10)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G10" s="9">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1</v>
+      </c>
+      <c r="J10" s="6">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6">
+        <v>1</v>
+      </c>
+      <c r="M10" s="6">
+        <v>1</v>
+      </c>
+      <c r="N10" s="6">
+        <f>SUM($D10:$M10)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="15"/>
-      <c r="D11" s="6"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G11" s="9"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1460,312 +2149,641 @@
         <v>15</v>
       </c>
       <c r="G13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="10">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="10">
-        <f>$B14/$G$8*$D$8</f>
-        <v>886.30217010320439</v>
+        <f>$B14/$N$8*$D$8</f>
+        <v>678.03679844278622</v>
       </c>
       <c r="E14" s="10">
-        <f>$B14/$G$8*$E$8</f>
-        <v>1159.6962288236441</v>
+        <f>$B14/$N$8*$E$8</f>
+        <v>887.18807725157069</v>
       </c>
       <c r="F14" s="10">
-        <f>$B14/$G$8*$F$8</f>
-        <v>1954.0016010731517</v>
+        <f>$B14/$N$8*$F$8</f>
+        <v>1494.8457021034301</v>
       </c>
       <c r="G14" s="10">
-        <f>$B14-SUM($D14:$F14)</f>
+        <f>$B14/$N$8*$G$8</f>
+        <v>660.75649335602054</v>
+      </c>
+      <c r="H14" s="10">
+        <f>$B14/$N$8*$H$8</f>
+        <v>996.43138527135363</v>
+      </c>
+      <c r="I14" s="10">
+        <f>$B14/$N$8*$I$8</f>
+        <v>1337.4029224240096</v>
+      </c>
+      <c r="J14" s="10">
+        <f>$B14/$N$8*$J$8</f>
+        <v>1390.3693747972377</v>
+      </c>
+      <c r="K14" s="10">
+        <f>$B14/$N$8*$K$8</f>
+        <v>575.34808890419026</v>
+      </c>
+      <c r="L14" s="10">
+        <f>$B14/$N$8*$L$8</f>
+        <v>721.6679135852329</v>
+      </c>
+      <c r="M14" s="10">
+        <f>$B14/$N$8*$M$8</f>
+        <v>1257.9532438641675</v>
+      </c>
+      <c r="N14" s="10">
+        <f>$B14-SUM($D14:$M14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B15" s="10">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="10">
-        <f>$B15/$G$6*$D$6</f>
-        <v>400</v>
+        <f>$B15/$N$6*$D$6</f>
+        <v>420</v>
       </c>
       <c r="E15" s="10">
-        <f>$B15/$G$6*$E$6</f>
-        <v>600</v>
+        <f>$B15/$N$6*$E$6</f>
+        <v>480</v>
       </c>
       <c r="F15" s="10">
-        <f>$B15/$G$6*$F$6</f>
-        <v>1000</v>
+        <f>$B15/$N$6*$F$6</f>
+        <v>750</v>
       </c>
       <c r="G15" s="10">
-        <f t="shared" ref="G15:G26" si="0">$B15-SUM($D15:$F15)</f>
+        <f>$B15/$N$6*$G$6</f>
+        <v>420</v>
+      </c>
+      <c r="H15" s="10">
+        <f>$B15/$N$6*$H$6</f>
+        <v>480</v>
+      </c>
+      <c r="I15" s="10">
+        <f>$B15/$N$6*$I$6</f>
+        <v>750</v>
+      </c>
+      <c r="J15" s="10">
+        <f>$B15/$N$6*$J$6</f>
+        <v>840</v>
+      </c>
+      <c r="K15" s="10">
+        <f>$B15/$N$6*$K$6</f>
+        <v>510</v>
+      </c>
+      <c r="L15" s="10">
+        <f>$B15/$N$6*$L$6</f>
+        <v>510</v>
+      </c>
+      <c r="M15" s="10">
+        <f>$B15/$N$6*$M$6</f>
+        <v>840</v>
+      </c>
+      <c r="N15" s="10">
+        <f>$B15-SUM($D15:$M15)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B16" s="10">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D16" s="10">
-        <f>$B16/$G$6*$D$6</f>
-        <v>40</v>
+        <f>$B16/$N$6*$D$6</f>
+        <v>42</v>
       </c>
       <c r="E16" s="10">
-        <f>$B16/$G$6*$E$6</f>
-        <v>60</v>
+        <f>$B16/$N$6*$E$6</f>
+        <v>48</v>
       </c>
       <c r="F16" s="10">
-        <f>$B16/$G$6*$F$6</f>
-        <v>100</v>
+        <f>$B16/$N$6*$F$6</f>
+        <v>75</v>
       </c>
       <c r="G16" s="10">
+        <f>$B16/$N$6*$G$6</f>
+        <v>42</v>
+      </c>
+      <c r="H16" s="10">
+        <f>$B16/$N$6*$H$6</f>
+        <v>48</v>
+      </c>
+      <c r="I16" s="10">
+        <f>$B16/$N$6*$I$6</f>
+        <v>75</v>
+      </c>
+      <c r="J16" s="10">
+        <f>$B16/$N$6*$J$6</f>
+        <v>84</v>
+      </c>
+      <c r="K16" s="10">
+        <f>$B16/$N$6*$K$6</f>
+        <v>51</v>
+      </c>
+      <c r="L16" s="10">
+        <f>$B16/$N$6*$L$6</f>
+        <v>51</v>
+      </c>
+      <c r="M16" s="10">
+        <f>$B16/$N$6*$M$6</f>
+        <v>84</v>
+      </c>
+      <c r="N16" s="10">
+        <f t="shared" ref="N16:N23" si="0">$B16-SUM($D16:$M16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="10">
+        <v>150</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="10">
+        <f>$B17/$N$6*$D$6</f>
+        <v>10.5</v>
+      </c>
+      <c r="E17" s="10">
+        <f>$B17/$N$6*$E$6</f>
+        <v>12</v>
+      </c>
+      <c r="F17" s="10">
+        <f>$B17/$N$6*$F$6</f>
+        <v>18.75</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" ref="G17:G19" si="1">$B17/$N$6*$G$6</f>
+        <v>10.5</v>
+      </c>
+      <c r="H17" s="10">
+        <f t="shared" ref="H17:H19" si="2">$B17/$N$6*$H$6</f>
+        <v>12</v>
+      </c>
+      <c r="I17" s="10">
+        <f>$B17/$N$6*$I$6</f>
+        <v>18.75</v>
+      </c>
+      <c r="J17" s="10">
+        <f>$B17/$N$6*$J$6</f>
+        <v>21</v>
+      </c>
+      <c r="K17" s="10">
+        <f>$B17/$N$6*$K$6</f>
+        <v>12.75</v>
+      </c>
+      <c r="L17" s="10">
+        <f>$B17/$N$6*$L$6</f>
+        <v>12.75</v>
+      </c>
+      <c r="M17" s="10">
+        <f>$B17/$N$6*$M$6</f>
+        <v>21</v>
+      </c>
+      <c r="N17" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="10">
-        <v>50</v>
-      </c>
-      <c r="C17" s="5" t="s">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="10">
+        <v>2400</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="10">
-        <f>$B17/$G$6*$D$6</f>
-        <v>10</v>
-      </c>
-      <c r="E17" s="10">
-        <f>$B17/$G$6*$E$6</f>
-        <v>15</v>
-      </c>
-      <c r="F17" s="10">
-        <f>$B17/$G$6*$F$6</f>
-        <v>25</v>
-      </c>
-      <c r="G17" s="10">
+      <c r="D18" s="10">
+        <f>$B18/$N$6*$D$6</f>
+        <v>168</v>
+      </c>
+      <c r="E18" s="10">
+        <f>$B18/$N$6*$E$6</f>
+        <v>192</v>
+      </c>
+      <c r="F18" s="10">
+        <f>$B18/$N$6*$F$6</f>
+        <v>300</v>
+      </c>
+      <c r="G18" s="10">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+      <c r="H18" s="10">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+      <c r="I18" s="10">
+        <f>$B18/$N$6*$I$6</f>
+        <v>300</v>
+      </c>
+      <c r="J18" s="10">
+        <f>$B18/$N$6*$J$6</f>
+        <v>336</v>
+      </c>
+      <c r="K18" s="10">
+        <f>$B18/$N$6*$K$6</f>
+        <v>204</v>
+      </c>
+      <c r="L18" s="10">
+        <f>$B18/$N$6*$L$6</f>
+        <v>204</v>
+      </c>
+      <c r="M18" s="10">
+        <f>$B18/$N$6*$M$6</f>
+        <v>336</v>
+      </c>
+      <c r="N18" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="10">
-        <v>800</v>
-      </c>
-      <c r="C18" s="5" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="10">
+        <v>900</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="10">
-        <f>$B18/$G$6*$D$6</f>
-        <v>160</v>
-      </c>
-      <c r="E18" s="10">
-        <f>$B18/$G$6*$E$6</f>
-        <v>240</v>
-      </c>
-      <c r="F18" s="10">
-        <f>$B18/$G$6*$F$6</f>
-        <v>400</v>
-      </c>
-      <c r="G18" s="10">
+      <c r="D19" s="10">
+        <f>$B19/$N$6*$D$6</f>
+        <v>63</v>
+      </c>
+      <c r="E19" s="10">
+        <f>$B19/$N$6*$E$6</f>
+        <v>72</v>
+      </c>
+      <c r="F19" s="10">
+        <f>$B19/$N$6*$F$6</f>
+        <v>112.5</v>
+      </c>
+      <c r="G19" s="10">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="H19" s="10">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="I19" s="10">
+        <f>$B19/$N$6*$I$6</f>
+        <v>112.5</v>
+      </c>
+      <c r="J19" s="10">
+        <f>$B19/$N$6*$J$6</f>
+        <v>126</v>
+      </c>
+      <c r="K19" s="10">
+        <f>$B19/$N$6*$K$6</f>
+        <v>76.5</v>
+      </c>
+      <c r="L19" s="10">
+        <f>$B19/$N$6*$L$6</f>
+        <v>76.5</v>
+      </c>
+      <c r="M19" s="10">
+        <f>$B19/$N$6*$M$6</f>
+        <v>126</v>
+      </c>
+      <c r="N19" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="10">
-        <v>300</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="10">
-        <f>$B19/$G$6*$D$6</f>
-        <v>60</v>
-      </c>
-      <c r="E19" s="10">
-        <f>$B19/$G$6*$E$6</f>
-        <v>90</v>
-      </c>
-      <c r="F19" s="10">
-        <f>$B19/$G$6*$F$6</f>
-        <v>150</v>
-      </c>
-      <c r="G19" s="10">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="10">
+        <v>1200</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="10">
+        <f>$B20/$N$9*$D$9</f>
+        <v>97.240164415736942</v>
+      </c>
+      <c r="E20" s="10">
+        <f>$B20/$N$9*$E$9</f>
+        <v>106.57662947739284</v>
+      </c>
+      <c r="F20" s="10">
+        <f>$B20/$N$9*$F$9</f>
+        <v>167.17557251908397</v>
+      </c>
+      <c r="G20" s="10">
+        <f>$B20/$N$9*$G$9</f>
+        <v>79.448032883147391</v>
+      </c>
+      <c r="H20" s="10">
+        <f>$B20/$N$9*$H$9</f>
+        <v>92.483852025836754</v>
+      </c>
+      <c r="I20" s="10">
+        <f>$B20/$N$9*$I$9</f>
+        <v>131.23899001761598</v>
+      </c>
+      <c r="J20" s="10">
+        <f>$B20/$N$9*$J$9</f>
+        <v>133.88138578978274</v>
+      </c>
+      <c r="K20" s="10">
+        <f>$B20/$N$9*$K$9</f>
+        <v>121.9906048150323</v>
+      </c>
+      <c r="L20" s="10">
+        <f>$B20/$N$9*$L$9</f>
+        <v>100.41103934233705</v>
+      </c>
+      <c r="M20" s="10">
+        <f>$B20/$N$9*$M$9</f>
+        <v>169.55372871403407</v>
+      </c>
+      <c r="N20" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="10">
-        <v>400</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="10">
-        <f>$B20/$G$9*$D$9</f>
-        <v>104.84330484330485</v>
-      </c>
-      <c r="E20" s="10">
-        <f>$B20/$G$9*$E$9</f>
-        <v>114.90978157644825</v>
-      </c>
-      <c r="F20" s="10">
-        <f>$B20/$G$9*$F$9</f>
-        <v>180.24691358024694</v>
-      </c>
-      <c r="G20" s="10">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="10">
+        <v>1500</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="10">
+        <f>$B21/$N$6*$D$6</f>
+        <v>105</v>
+      </c>
+      <c r="E21" s="10">
+        <f>$B21/$N$6*$E$6</f>
+        <v>120</v>
+      </c>
+      <c r="F21" s="10">
+        <f>$B21/$N$6*$F$6</f>
+        <v>187.5</v>
+      </c>
+      <c r="G21" s="10">
+        <f>$B21/$N$6*$G$6</f>
+        <v>105</v>
+      </c>
+      <c r="H21" s="10">
+        <f>$B21/$N$6*$H$6</f>
+        <v>120</v>
+      </c>
+      <c r="I21" s="10">
+        <f>$B21/$N$6*$I$6</f>
+        <v>187.5</v>
+      </c>
+      <c r="J21" s="10">
+        <f>$B21/$N$6*$J$6</f>
+        <v>210</v>
+      </c>
+      <c r="K21" s="10">
+        <f>$B21/$N$6*$K$6</f>
+        <v>127.5</v>
+      </c>
+      <c r="L21" s="10">
+        <f>$B21/$N$6*$L$6</f>
+        <v>127.5</v>
+      </c>
+      <c r="M21" s="10">
+        <f>$B21/$N$6*$M$6</f>
+        <v>210</v>
+      </c>
+      <c r="N21" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="10">
-        <v>500</v>
-      </c>
-      <c r="C21" s="5" t="s">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="10">
+        <v>190</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="10">
-        <f>$B21/$G$6*$D$6</f>
-        <v>100</v>
-      </c>
-      <c r="E21" s="10">
-        <f>$B21/$G$6*$E$6</f>
-        <v>150</v>
-      </c>
-      <c r="F21" s="10">
-        <f>$B21/$G$6*$F$6</f>
-        <v>250</v>
-      </c>
-      <c r="G21" s="10">
+      <c r="D22" s="10">
+        <f>$B22/$N$6*$D$6</f>
+        <v>13.3</v>
+      </c>
+      <c r="E22" s="10">
+        <f>$B22/$N$6*$E$6</f>
+        <v>15.2</v>
+      </c>
+      <c r="F22" s="10">
+        <f>$B22/$N$6*$F$6</f>
+        <v>23.75</v>
+      </c>
+      <c r="G22" s="10">
+        <f>$B22/$N$6*$G$6</f>
+        <v>13.3</v>
+      </c>
+      <c r="H22" s="10">
+        <f>$B22/$N$6*$H$6</f>
+        <v>15.2</v>
+      </c>
+      <c r="I22" s="10">
+        <f>$B22/$N$6*$I$6</f>
+        <v>23.75</v>
+      </c>
+      <c r="J22" s="10">
+        <f>$B22/$N$6*$J$6</f>
+        <v>26.6</v>
+      </c>
+      <c r="K22" s="10">
+        <f>$B22/$N$6*$K$6</f>
+        <v>16.149999999999999</v>
+      </c>
+      <c r="L22" s="10">
+        <f>$B22/$N$6*$L$6</f>
+        <v>16.149999999999999</v>
+      </c>
+      <c r="M22" s="10">
+        <f>$B22/$N$6*$M$6</f>
+        <v>26.6</v>
+      </c>
+      <c r="N22" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="10">
-        <v>100</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="10">
-        <f>$B22/$G$6*$D$6</f>
-        <v>20</v>
-      </c>
-      <c r="E22" s="10">
-        <f>$B22/$G$6*$E$6</f>
-        <v>30</v>
-      </c>
-      <c r="F22" s="10">
-        <f>$B22/$G$6*$F$6</f>
-        <v>50</v>
-      </c>
-      <c r="G22" s="10">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="10">
+        <v>3750</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="10">
+        <f>$B23/$N$10*$D$10</f>
+        <v>375</v>
+      </c>
+      <c r="E23" s="10">
+        <f>$B23/$N$10*$E$10</f>
+        <v>375</v>
+      </c>
+      <c r="F23" s="10">
+        <f>$B23/$N$10*$F$10</f>
+        <v>375</v>
+      </c>
+      <c r="G23" s="10">
+        <f>$B23/$N$10*$G$10</f>
+        <v>375</v>
+      </c>
+      <c r="H23" s="10">
+        <f>$B23/$N$10*$H$10</f>
+        <v>375</v>
+      </c>
+      <c r="I23" s="10">
+        <f>$B23/$N$10*$I$10</f>
+        <v>375</v>
+      </c>
+      <c r="J23" s="10">
+        <f>$B23/$N$10*$J$10</f>
+        <v>375</v>
+      </c>
+      <c r="K23" s="10">
+        <f>$B23/$N$10*$K$10</f>
+        <v>375</v>
+      </c>
+      <c r="L23" s="10">
+        <f>$B23/$N$10*$L$10</f>
+        <v>375</v>
+      </c>
+      <c r="M23" s="10">
+        <f>$B23/$N$10*$M$10</f>
+        <v>375</v>
+      </c>
+      <c r="N23" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="10">
-        <v>1250</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="10">
-        <f>$B23/$G$10*$D$10</f>
-        <v>416.66666666666669</v>
-      </c>
-      <c r="E23" s="10">
-        <f>$B23/$G$10*$E$10</f>
-        <v>416.66666666666669</v>
-      </c>
-      <c r="F23" s="10">
-        <f>$B23/$G$10*$F$10</f>
-        <v>416.66666666666669</v>
-      </c>
-      <c r="G23" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B24" s="11">
         <f>SUBTOTAL(109,B14:B23)</f>
-        <v>9600</v>
+        <v>26690</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="11">
         <f>SUBTOTAL(109,D14:D23)</f>
-        <v>2197.8121416131758</v>
+        <v>1972.0769628585231</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" ref="E24" si="1">SUBTOTAL(109,E14:E23)</f>
-        <v>2876.2726770667587</v>
+        <f t="shared" ref="E24:F24" si="3">SUBTOTAL(109,E14:E23)</f>
+        <v>2307.9647067289634</v>
       </c>
       <c r="F24" s="11">
-        <f>SUBTOTAL(109,F14:F23)</f>
-        <v>4525.9151813200651</v>
+        <f t="shared" si="3"/>
+        <v>3504.5212746225143</v>
       </c>
       <c r="G24" s="11">
-        <f t="shared" si="0"/>
+        <f>SUBTOTAL(109,G14:G23)</f>
+        <v>1937.0045262391679</v>
+      </c>
+      <c r="H24" s="11">
+        <f t="shared" ref="H24:J24" si="4">SUBTOTAL(109,H14:H23)</f>
+        <v>2403.1152372971901</v>
+      </c>
+      <c r="I24" s="11">
+        <f t="shared" si="4"/>
+        <v>3311.1419124416252</v>
+      </c>
+      <c r="J24" s="11">
+        <f t="shared" si="4"/>
+        <v>3542.85076058702</v>
+      </c>
+      <c r="K24" s="11">
+        <f>SUBTOTAL(109,K14:K23)</f>
+        <v>2070.2386937192227</v>
+      </c>
+      <c r="L24" s="11">
+        <f t="shared" ref="L24:M24" si="5">SUBTOTAL(109,L14:L23)</f>
+        <v>2194.9789529275699</v>
+      </c>
+      <c r="M24" s="11">
+        <f t="shared" si="5"/>
+        <v>3446.1069725782013</v>
+      </c>
+      <c r="N24" s="21">
+        <f>$B24-SUM($D24:$M24)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B25" s="12">
-        <f>SUM($D25:$F25)</f>
-        <v>-9200</v>
+        <f>SUM($D25:$M25)</f>
+        <v>-31800</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="12">
@@ -1778,37 +2796,86 @@
         <v>-4200</v>
       </c>
       <c r="G25" s="12">
-        <f t="shared" si="0"/>
+        <v>-2000</v>
+      </c>
+      <c r="H25" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="I25" s="12">
+        <v>-4200</v>
+      </c>
+      <c r="J25" s="12">
+        <v>-4200</v>
+      </c>
+      <c r="K25" s="12">
+        <v>-2000</v>
+      </c>
+      <c r="L25" s="12">
+        <v>-3000</v>
+      </c>
+      <c r="M25" s="12">
+        <v>-4200</v>
+      </c>
+      <c r="N25" s="12">
+        <f>$B25-SUM($D25:$M25)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B26" s="10">
-        <f>SUM($D26:$F26)</f>
-        <v>399.99999999999955</v>
+        <f>SUM($D26:$M26)</f>
+        <v>-5110.0000000000018</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="10">
         <f>$D24+$D25</f>
-        <v>197.81214161317575</v>
+        <v>-27.923037141476925</v>
       </c>
       <c r="E26" s="10">
         <f>$E24+$E25</f>
-        <v>-123.72732293324134</v>
+        <v>-692.03529327103661</v>
       </c>
       <c r="F26" s="10">
         <f>$F24+$F25</f>
-        <v>325.91518132006513</v>
+        <v>-695.47872537748572</v>
       </c>
       <c r="G26" s="10">
-        <f t="shared" si="0"/>
+        <f>$G24+$G25</f>
+        <v>-62.995473760832056</v>
+      </c>
+      <c r="H26" s="10">
+        <f>$H24+$H25</f>
+        <v>-596.88476270280989</v>
+      </c>
+      <c r="I26" s="10">
+        <f>$I24+$I25</f>
+        <v>-888.85808755837479</v>
+      </c>
+      <c r="J26" s="10">
+        <f>$J24+$J25</f>
+        <v>-657.14923941298002</v>
+      </c>
+      <c r="K26" s="10">
+        <f>$K24+$K25</f>
+        <v>70.238693719222738</v>
+      </c>
+      <c r="L26" s="10">
+        <f>$L24+$L25</f>
+        <v>-805.02104707243006</v>
+      </c>
+      <c r="M26" s="10">
+        <f>$M24+$M25</f>
+        <v>-753.89302742179871</v>
+      </c>
+      <c r="N26" s="10">
+        <f>$B26-SUM($D26:$M26)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
@@ -1825,7 +2892,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>29</v>
       </c>
@@ -1834,17 +2901,17 @@
       </c>
       <c r="C29" s="10">
         <f>$F$24/12*10</f>
-        <v>3771.5959844333879</v>
+        <v>2920.4343955187619</v>
       </c>
       <c r="D29" s="10">
         <v>-3500</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" ref="E29:E30" si="2">$C29+$D29</f>
-        <v>271.59598443338791</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <f t="shared" ref="E29:E30" si="6">$C29+$D29</f>
+        <v>-579.5656044812381</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>30</v>
       </c>
@@ -1853,18 +2920,19 @@
       </c>
       <c r="C30" s="10">
         <f>$F$24/12*2</f>
-        <v>754.31919688667756</v>
+        <v>584.08687910375238</v>
       </c>
       <c r="D30" s="10">
         <v>-700</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="2"/>
-        <v>54.31919688667756</v>
+        <f t="shared" si="6"/>
+        <v>-115.91312089624762</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="A5:C5"/>
@@ -1872,9 +2940,8 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
   </mergeCells>
-  <conditionalFormatting sqref="D26:F26">
+  <conditionalFormatting sqref="E29:E30">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -1882,7 +2949,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E29:E30">
+  <conditionalFormatting sqref="D26:M26">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
+++ b/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\realestate\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FF7200-F039-40C8-9091-DCCA1A1E157C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBD4590-EDC5-403F-A7EC-1F38166EA2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
   </bookViews>
@@ -126,12 +126,6 @@
     <t>Calcolo prorata</t>
   </si>
   <si>
-    <t>Inquilino 1</t>
-  </si>
-  <si>
-    <t>Inquilino 2</t>
-  </si>
-  <si>
     <t>Mesi</t>
   </si>
   <si>
@@ -169,6 +163,12 @@
   </si>
   <si>
     <t>App. 10</t>
+  </si>
+  <si>
+    <t>Comproprietario 1</t>
+  </si>
+  <si>
+    <t>Comproprietario 2</t>
   </si>
 </sst>
 </file>
@@ -339,6 +339,9 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -363,34 +366,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -406,6 +386,9 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
@@ -413,6 +396,9 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
@@ -803,11 +789,11 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
@@ -818,36 +804,36 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="15"/>
+      <c r="A6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="9">
         <v>70</v>
       </c>
@@ -884,11 +870,11 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="9">
         <v>54</v>
       </c>
@@ -925,11 +911,11 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="9">
         <v>10241</v>
       </c>
@@ -966,11 +952,11 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="9">
         <v>1104</v>
       </c>
@@ -1007,11 +993,11 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="9">
         <v>1</v>
       </c>
@@ -1048,11 +1034,11 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="9"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -1085,28 +1071,28 @@
         <v>15</v>
       </c>
       <c r="G13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="N13" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1172,7 +1158,7 @@
         <v>6000</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" s="10">
         <f>$B15/$N$6*$D$6</f>
@@ -1227,7 +1213,7 @@
         <v>600</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" s="10">
         <f>$B16/$N$6*$D$6</f>
@@ -1282,7 +1268,7 @@
         <v>150</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" s="10">
         <f>$B17/$N$6*$D$6</f>
@@ -1337,7 +1323,7 @@
         <v>2400</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" s="10">
         <f>$B18/$N$6*$D$6</f>
@@ -1392,7 +1378,7 @@
         <v>900</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19" s="10">
         <f>$B19/$N$6*$D$6</f>
@@ -1502,7 +1488,7 @@
         <v>1500</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" s="10">
         <f>$B21/$N$6*$D$6</f>
@@ -1557,7 +1543,7 @@
         <v>190</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D22" s="10">
         <f>$B22/$N$6*$D$6</f>
@@ -1667,7 +1653,7 @@
         <f>SUBTOTAL(109,B14:B23)</f>
         <v>26690</v>
       </c>
-      <c r="C24" s="16"/>
+      <c r="C24" s="17"/>
       <c r="D24" s="11">
         <f>SUBTOTAL(109,D14:D23)</f>
         <v>1972.0769628585231</v>
@@ -1708,7 +1694,7 @@
         <f t="shared" si="5"/>
         <v>3446.1069725782013</v>
       </c>
-      <c r="N24" s="21">
+      <c r="N24" s="13">
         <f>$B24-SUM($D24:$M24)</f>
         <v>0</v>
       </c>
@@ -1721,7 +1707,7 @@
         <f>SUM($D25:$M25)</f>
         <v>-31800</v>
       </c>
-      <c r="C25" s="17"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="12">
         <v>-2000</v>
       </c>
@@ -1765,7 +1751,7 @@
         <f>SUM($D26:$M26)</f>
         <v>-5110.0000000000018</v>
       </c>
-      <c r="C26" s="17"/>
+      <c r="C26" s="18"/>
       <c r="D26" s="10">
         <f>$D24+$D25</f>
         <v>-27.923037141476925</v>
@@ -1823,10 +1809,10 @@
     <mergeCell ref="A10:C10"/>
   </mergeCells>
   <conditionalFormatting sqref="D26:M26">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1867,11 +1853,11 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
@@ -1882,36 +1868,36 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="15"/>
+      <c r="A6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="9">
         <v>70</v>
       </c>
@@ -1948,11 +1934,11 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="9">
         <v>54</v>
       </c>
@@ -1989,11 +1975,11 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="9">
         <v>10241</v>
       </c>
@@ -2030,11 +2016,11 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="9">
         <v>1104</v>
       </c>
@@ -2071,11 +2057,11 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="9">
         <v>1</v>
       </c>
@@ -2112,11 +2098,11 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="9"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -2149,28 +2135,28 @@
         <v>15</v>
       </c>
       <c r="G13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="N13" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2236,7 +2222,7 @@
         <v>6000</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" s="10">
         <f>$B15/$N$6*$D$6</f>
@@ -2291,7 +2277,7 @@
         <v>600</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" s="10">
         <f>$B16/$N$6*$D$6</f>
@@ -2346,7 +2332,7 @@
         <v>150</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" s="10">
         <f>$B17/$N$6*$D$6</f>
@@ -2401,7 +2387,7 @@
         <v>2400</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" s="10">
         <f>$B18/$N$6*$D$6</f>
@@ -2456,7 +2442,7 @@
         <v>900</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19" s="10">
         <f>$B19/$N$6*$D$6</f>
@@ -2566,7 +2552,7 @@
         <v>1500</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" s="10">
         <f>$B21/$N$6*$D$6</f>
@@ -2621,7 +2607,7 @@
         <v>190</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D22" s="10">
         <f>$B22/$N$6*$D$6</f>
@@ -2731,7 +2717,7 @@
         <f>SUBTOTAL(109,B14:B23)</f>
         <v>26690</v>
       </c>
-      <c r="C24" s="16"/>
+      <c r="C24" s="17"/>
       <c r="D24" s="11">
         <f>SUBTOTAL(109,D14:D23)</f>
         <v>1972.0769628585231</v>
@@ -2772,7 +2758,7 @@
         <f t="shared" si="5"/>
         <v>3446.1069725782013</v>
       </c>
-      <c r="N24" s="21">
+      <c r="N24" s="13">
         <f>$B24-SUM($D24:$M24)</f>
         <v>0</v>
       </c>
@@ -2785,7 +2771,7 @@
         <f>SUM($D25:$M25)</f>
         <v>-31800</v>
       </c>
-      <c r="C25" s="17"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="12">
         <v>-2000</v>
       </c>
@@ -2829,7 +2815,7 @@
         <f>SUM($D26:$M26)</f>
         <v>-5110.0000000000018</v>
       </c>
-      <c r="C26" s="17"/>
+      <c r="C26" s="18"/>
       <c r="D26" s="10">
         <f>$D24+$D25</f>
         <v>-27.923037141476925</v>
@@ -2880,21 +2866,21 @@
         <v>28</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B29" s="6">
         <v>10</v>
@@ -2913,7 +2899,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B30" s="6">
         <v>2</v>
@@ -2941,19 +2927,19 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
   </mergeCells>
-  <conditionalFormatting sqref="E29:E30">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="D26:M26">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D26:M26">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="E29:E30">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
+++ b/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\realestate\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBD4590-EDC5-403F-A7EC-1F38166EA2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144F30D0-2F9D-48E1-8692-E4724BE643B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
   </bookViews>

--- a/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
+++ b/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\realestate\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144F30D0-2F9D-48E1-8692-E4724BE643B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CFDBED-0A4F-4269-9EF6-4F78BEA38C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
+    <workbookView xWindow="57480" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
   </bookViews>
   <sheets>
     <sheet name="Conguagli spese" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="43">
   <si>
     <t>Riscaldamento</t>
   </si>
@@ -96,21 +96,12 @@
     <t>Totale</t>
   </si>
   <si>
-    <t>Stabile Cedro</t>
-  </si>
-  <si>
-    <t>Ripartizione delle spese di riscaldamento e accessorie</t>
-  </si>
-  <si>
     <t>Periodo:</t>
   </si>
   <si>
     <t>Tipo di ripartizione</t>
   </si>
   <si>
-    <t>consumo</t>
-  </si>
-  <si>
     <t>altro</t>
   </si>
   <si>
@@ -165,10 +156,16 @@
     <t>App. 10</t>
   </si>
   <si>
-    <t>Comproprietario 1</t>
-  </si>
-  <si>
-    <t>Comproprietario 2</t>
+    <t>Suddivisione delle spese ai proprietari</t>
+  </si>
+  <si>
+    <t>Nome Stabile</t>
+  </si>
+  <si>
+    <t>Proprietario 1</t>
+  </si>
+  <si>
+    <t>Proprietario 2</t>
   </si>
 </sst>
 </file>
@@ -370,7 +367,27 @@
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -765,32 +782,33 @@
   <cols>
     <col min="1" max="1" width="24.88671875" customWidth="1"/>
     <col min="2" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="14" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>45292</v>
+        <v>46023</v>
       </c>
       <c r="C3" s="2">
-        <v>45657</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="21"/>
@@ -804,25 +822,25 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>18</v>
@@ -830,7 +848,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="16"/>
@@ -875,122 +893,53 @@
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="16"/>
-      <c r="D7" s="9">
-        <v>54</v>
-      </c>
-      <c r="E7" s="6">
-        <v>85</v>
-      </c>
-      <c r="F7" s="6">
-        <v>124</v>
-      </c>
-      <c r="G7" s="9">
-        <v>54</v>
-      </c>
-      <c r="H7" s="6">
-        <v>85</v>
-      </c>
-      <c r="I7" s="6">
-        <v>124</v>
-      </c>
-      <c r="J7" s="6">
-        <v>130</v>
-      </c>
-      <c r="K7" s="9">
-        <v>95</v>
-      </c>
-      <c r="L7" s="6">
-        <v>95</v>
-      </c>
-      <c r="M7" s="6">
-        <v>130</v>
-      </c>
-      <c r="N7" s="6">
-        <f>SUM($D7:$M7)</f>
-        <v>976</v>
-      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="16"/>
-      <c r="D8" s="9">
-        <v>10241</v>
-      </c>
-      <c r="E8" s="6">
-        <v>13400</v>
-      </c>
-      <c r="F8" s="6">
-        <v>22578</v>
-      </c>
-      <c r="G8" s="9">
-        <v>9980</v>
-      </c>
-      <c r="H8" s="6">
-        <v>15050</v>
-      </c>
-      <c r="I8" s="6">
-        <v>20200</v>
-      </c>
-      <c r="J8" s="6">
-        <v>21000</v>
-      </c>
-      <c r="K8" s="9">
-        <v>8690</v>
-      </c>
-      <c r="L8" s="6">
-        <v>10900</v>
-      </c>
-      <c r="M8" s="6">
-        <v>19000</v>
-      </c>
-      <c r="N8" s="6">
-        <f>SUM($D8:$M8)</f>
-        <v>151039</v>
-      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
-      <c r="D9" s="9">
-        <v>1104</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1210</v>
-      </c>
-      <c r="F9" s="6">
-        <v>1898</v>
-      </c>
-      <c r="G9" s="9">
-        <v>902</v>
-      </c>
-      <c r="H9" s="6">
-        <v>1050</v>
-      </c>
-      <c r="I9" s="6">
-        <v>1490</v>
-      </c>
-      <c r="J9" s="6">
-        <v>1520</v>
-      </c>
-      <c r="K9" s="9">
-        <v>1385</v>
-      </c>
-      <c r="L9" s="6">
-        <v>1140</v>
-      </c>
-      <c r="M9" s="6">
-        <v>1925</v>
-      </c>
-      <c r="N9" s="6">
-        <f>SUM($D9:$M9)</f>
-        <v>13624</v>
-      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
@@ -1029,13 +978,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6">
-        <f>SUM($D10:$M10)</f>
+        <f>SUM(D10:M10)</f>
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="16"/>
@@ -1059,7 +1008,7 @@
         <v>18</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>13</v>
@@ -1071,28 +1020,28 @@
         <v>15</v>
       </c>
       <c r="G13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="N13" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1103,51 +1052,51 @@
         <v>10000</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D14" s="10">
-        <f>$B14/$N$8*$D$8</f>
-        <v>678.03679844278622</v>
+        <f>$B14/$N$6*$D$6</f>
+        <v>700</v>
       </c>
       <c r="E14" s="10">
-        <f>$B14/$N$8*$E$8</f>
-        <v>887.18807725157069</v>
+        <f>$B14/$N$6*$E$6</f>
+        <v>800</v>
       </c>
       <c r="F14" s="10">
-        <f>$B14/$N$8*$F$8</f>
-        <v>1494.8457021034301</v>
+        <f t="shared" ref="F14:M14" si="0">$B14/$N$6*$D$6</f>
+        <v>700</v>
       </c>
       <c r="G14" s="10">
-        <f>$B14/$N$8*$G$8</f>
-        <v>660.75649335602054</v>
+        <f t="shared" ref="G14:M14" si="1">$B14/$N$6*$E$6</f>
+        <v>800</v>
       </c>
       <c r="H14" s="10">
-        <f>$B14/$N$8*$H$8</f>
-        <v>996.43138527135363</v>
+        <f t="shared" ref="H14:M14" si="2">$B14/$N$6*$D$6</f>
+        <v>700</v>
       </c>
       <c r="I14" s="10">
-        <f>$B14/$N$8*$I$8</f>
-        <v>1337.4029224240096</v>
+        <f t="shared" ref="I14:M14" si="3">$B14/$N$6*$E$6</f>
+        <v>800</v>
       </c>
       <c r="J14" s="10">
-        <f>$B14/$N$8*$J$8</f>
-        <v>1390.3693747972377</v>
+        <f t="shared" ref="J14:M14" si="4">$B14/$N$6*$D$6</f>
+        <v>700</v>
       </c>
       <c r="K14" s="10">
-        <f>$B14/$N$8*$K$8</f>
-        <v>575.34808890419026</v>
+        <f t="shared" ref="K14:M14" si="5">$B14/$N$6*$E$6</f>
+        <v>800</v>
       </c>
       <c r="L14" s="10">
-        <f>$B14/$N$8*$L$8</f>
-        <v>721.6679135852329</v>
+        <f t="shared" ref="L14:M14" si="6">$B14/$N$6*$D$6</f>
+        <v>700</v>
       </c>
       <c r="M14" s="10">
-        <f>$B14/$N$8*$M$8</f>
-        <v>1257.9532438641675</v>
+        <f t="shared" ref="M14" si="7">$B14/$N$6*$E$6</f>
+        <v>800</v>
       </c>
       <c r="N14" s="10">
         <f>$B14-SUM($D14:$M14)</f>
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1158,7 +1107,7 @@
         <v>6000</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D15" s="10">
         <f>$B15/$N$6*$D$6</f>
@@ -1213,7 +1162,7 @@
         <v>600</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D16" s="10">
         <f>$B16/$N$6*$D$6</f>
@@ -1256,7 +1205,7 @@
         <v>84</v>
       </c>
       <c r="N16" s="10">
-        <f t="shared" ref="N16:N23" si="0">$B16-SUM($D16:$M16)</f>
+        <f t="shared" ref="N16:N23" si="8">$B16-SUM($D16:$M16)</f>
         <v>0</v>
       </c>
     </row>
@@ -1268,7 +1217,7 @@
         <v>150</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D17" s="10">
         <f>$B17/$N$6*$D$6</f>
@@ -1283,11 +1232,11 @@
         <v>18.75</v>
       </c>
       <c r="G17" s="10">
-        <f t="shared" ref="G17:G19" si="1">$B17/$N$6*$G$6</f>
+        <f t="shared" ref="G17:G19" si="9">$B17/$N$6*$G$6</f>
         <v>10.5</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" ref="H17:H19" si="2">$B17/$N$6*$H$6</f>
+        <f t="shared" ref="H17:H19" si="10">$B17/$N$6*$H$6</f>
         <v>12</v>
       </c>
       <c r="I17" s="10">
@@ -1311,7 +1260,7 @@
         <v>21</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -1323,7 +1272,7 @@
         <v>2400</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D18" s="10">
         <f>$B18/$N$6*$D$6</f>
@@ -1338,11 +1287,11 @@
         <v>300</v>
       </c>
       <c r="G18" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>168</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>192</v>
       </c>
       <c r="I18" s="10">
@@ -1366,7 +1315,7 @@
         <v>336</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -1378,7 +1327,7 @@
         <v>900</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D19" s="10">
         <f>$B19/$N$6*$D$6</f>
@@ -1393,11 +1342,11 @@
         <v>112.5</v>
       </c>
       <c r="G19" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>63</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>72</v>
       </c>
       <c r="I19" s="10">
@@ -1421,7 +1370,7 @@
         <v>126</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -1433,51 +1382,51 @@
         <v>1200</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D20" s="10">
-        <f>$B20/$N$9*$D$9</f>
-        <v>97.240164415736942</v>
+        <f>$B20/$N$6*$D$6</f>
+        <v>84</v>
       </c>
       <c r="E20" s="10">
-        <f>$B20/$N$9*$E$9</f>
-        <v>106.57662947739284</v>
+        <f>$B20/$N$6*$E$6</f>
+        <v>96</v>
       </c>
       <c r="F20" s="10">
-        <f>$B20/$N$9*$F$9</f>
-        <v>167.17557251908397</v>
+        <f t="shared" ref="F20:M20" si="11">$B20/$N$6*$D$6</f>
+        <v>84</v>
       </c>
       <c r="G20" s="10">
-        <f>$B20/$N$9*$G$9</f>
-        <v>79.448032883147391</v>
+        <f t="shared" ref="G20:M20" si="12">$B20/$N$6*$E$6</f>
+        <v>96</v>
       </c>
       <c r="H20" s="10">
-        <f>$B20/$N$9*$H$9</f>
-        <v>92.483852025836754</v>
+        <f t="shared" ref="H20:M20" si="13">$B20/$N$6*$D$6</f>
+        <v>84</v>
       </c>
       <c r="I20" s="10">
-        <f>$B20/$N$9*$I$9</f>
-        <v>131.23899001761598</v>
+        <f t="shared" ref="I20:M20" si="14">$B20/$N$6*$E$6</f>
+        <v>96</v>
       </c>
       <c r="J20" s="10">
-        <f>$B20/$N$9*$J$9</f>
-        <v>133.88138578978274</v>
+        <f t="shared" ref="J20:M20" si="15">$B20/$N$6*$D$6</f>
+        <v>84</v>
       </c>
       <c r="K20" s="10">
-        <f>$B20/$N$9*$K$9</f>
-        <v>121.9906048150323</v>
+        <f t="shared" ref="K20:M20" si="16">$B20/$N$6*$E$6</f>
+        <v>96</v>
       </c>
       <c r="L20" s="10">
-        <f>$B20/$N$9*$L$9</f>
-        <v>100.41103934233705</v>
+        <f t="shared" ref="L20:M20" si="17">$B20/$N$6*$D$6</f>
+        <v>84</v>
       </c>
       <c r="M20" s="10">
-        <f>$B20/$N$9*$M$9</f>
-        <v>169.55372871403407</v>
+        <f t="shared" ref="M20" si="18">$B20/$N$6*$E$6</f>
+        <v>96</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1488,7 +1437,7 @@
         <v>1500</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D21" s="10">
         <f>$B21/$N$6*$D$6</f>
@@ -1531,7 +1480,7 @@
         <v>210</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -1543,7 +1492,7 @@
         <v>190</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D22" s="10">
         <f>$B22/$N$6*$D$6</f>
@@ -1586,7 +1535,7 @@
         <v>26.6</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -1641,7 +1590,7 @@
         <v>375</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -1656,47 +1605,47 @@
       <c r="C24" s="17"/>
       <c r="D24" s="11">
         <f>SUBTOTAL(109,D14:D23)</f>
-        <v>1972.0769628585231</v>
+        <v>1980.8</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" ref="E24:F24" si="3">SUBTOTAL(109,E14:E23)</f>
-        <v>2307.9647067289634</v>
+        <f t="shared" ref="E24:F24" si="19">SUBTOTAL(109,E14:E23)</f>
+        <v>2210.1999999999998</v>
       </c>
       <c r="F24" s="11">
-        <f t="shared" si="3"/>
-        <v>3504.5212746225143</v>
+        <f t="shared" si="19"/>
+        <v>2626.5</v>
       </c>
       <c r="G24" s="11">
         <f>SUBTOTAL(109,G14:G23)</f>
-        <v>1937.0045262391679</v>
+        <v>2092.8000000000002</v>
       </c>
       <c r="H24" s="11">
-        <f t="shared" ref="H24:J24" si="4">SUBTOTAL(109,H14:H23)</f>
-        <v>2403.1152372971901</v>
+        <f t="shared" ref="H24:J24" si="20">SUBTOTAL(109,H14:H23)</f>
+        <v>2098.1999999999998</v>
       </c>
       <c r="I24" s="11">
-        <f t="shared" si="4"/>
-        <v>3311.1419124416252</v>
+        <f t="shared" si="20"/>
+        <v>2738.5</v>
       </c>
       <c r="J24" s="11">
-        <f t="shared" si="4"/>
-        <v>3542.85076058702</v>
+        <f t="shared" si="20"/>
+        <v>2802.6</v>
       </c>
       <c r="K24" s="11">
         <f>SUBTOTAL(109,K14:K23)</f>
-        <v>2070.2386937192227</v>
+        <v>2268.9</v>
       </c>
       <c r="L24" s="11">
-        <f t="shared" ref="L24:M24" si="5">SUBTOTAL(109,L14:L23)</f>
-        <v>2194.9789529275699</v>
+        <f t="shared" ref="L24:M24" si="21">SUBTOTAL(109,L14:L23)</f>
+        <v>2156.9</v>
       </c>
       <c r="M24" s="11">
-        <f t="shared" si="5"/>
-        <v>3446.1069725782013</v>
+        <f t="shared" si="21"/>
+        <v>2914.6</v>
       </c>
       <c r="N24" s="13">
         <f>$B24-SUM($D24:$M24)</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1705,38 +1654,38 @@
       </c>
       <c r="B25" s="12">
         <f>SUM($D25:$M25)</f>
-        <v>-31800</v>
+        <v>-23500</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="12">
+        <v>-1500</v>
+      </c>
+      <c r="E25" s="12">
         <v>-2000</v>
       </c>
-      <c r="E25" s="12">
+      <c r="F25" s="12">
         <v>-3000</v>
       </c>
-      <c r="F25" s="12">
-        <v>-4200</v>
-      </c>
       <c r="G25" s="12">
+        <v>-1500</v>
+      </c>
+      <c r="H25" s="12">
         <v>-2000</v>
       </c>
-      <c r="H25" s="12">
+      <c r="I25" s="12">
         <v>-3000</v>
       </c>
-      <c r="I25" s="12">
-        <v>-4200</v>
-      </c>
       <c r="J25" s="12">
-        <v>-4200</v>
+        <v>-3000</v>
       </c>
       <c r="K25" s="12">
         <v>-2000</v>
       </c>
       <c r="L25" s="12">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="M25" s="12">
-        <v>-4200</v>
+        <v>-3500</v>
       </c>
       <c r="N25" s="12">
         <f>$B25-SUM($D25:$M25)</f>
@@ -1749,48 +1698,48 @@
       </c>
       <c r="B26" s="10">
         <f>SUM($D26:$M26)</f>
-        <v>-5110.0000000000018</v>
+        <v>389.99999999999977</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="10">
         <f>$D24+$D25</f>
-        <v>-27.923037141476925</v>
+        <v>480.79999999999995</v>
       </c>
       <c r="E26" s="10">
         <f>$E24+$E25</f>
-        <v>-692.03529327103661</v>
+        <v>210.19999999999982</v>
       </c>
       <c r="F26" s="10">
         <f>$F24+$F25</f>
-        <v>-695.47872537748572</v>
+        <v>-373.5</v>
       </c>
       <c r="G26" s="10">
         <f>$G24+$G25</f>
-        <v>-62.995473760832056</v>
+        <v>592.80000000000018</v>
       </c>
       <c r="H26" s="10">
         <f>$H24+$H25</f>
-        <v>-596.88476270280989</v>
+        <v>98.199999999999818</v>
       </c>
       <c r="I26" s="10">
         <f>$I24+$I25</f>
-        <v>-888.85808755837479</v>
+        <v>-261.5</v>
       </c>
       <c r="J26" s="10">
         <f>$J24+$J25</f>
-        <v>-657.14923941298002</v>
+        <v>-197.40000000000009</v>
       </c>
       <c r="K26" s="10">
         <f>$K24+$K25</f>
-        <v>70.238693719222738</v>
+        <v>268.90000000000009</v>
       </c>
       <c r="L26" s="10">
         <f>$L24+$L25</f>
-        <v>-805.02104707243006</v>
+        <v>156.90000000000009</v>
       </c>
       <c r="M26" s="10">
         <f>$M24+$M25</f>
-        <v>-753.89302742179871</v>
+        <v>-585.40000000000009</v>
       </c>
       <c r="N26" s="10">
         <f>$B26-SUM($D26:$M26)</f>
@@ -1809,15 +1758,18 @@
     <mergeCell ref="A10:C10"/>
   </mergeCells>
   <conditionalFormatting sqref="D26:M26">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="E20:M20 E14:M14" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1826,35 +1778,35 @@
   <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.88671875" customWidth="1"/>
     <col min="2" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" customWidth="1"/>
+    <col min="4" max="14" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>45292</v>
+        <v>46023</v>
       </c>
       <c r="C3" s="2">
-        <v>45657</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="21"/>
@@ -1868,25 +1820,25 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>18</v>
@@ -1894,7 +1846,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="16"/>
@@ -1939,122 +1891,53 @@
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="16"/>
-      <c r="D7" s="9">
-        <v>54</v>
-      </c>
-      <c r="E7" s="6">
-        <v>85</v>
-      </c>
-      <c r="F7" s="6">
-        <v>124</v>
-      </c>
-      <c r="G7" s="9">
-        <v>54</v>
-      </c>
-      <c r="H7" s="6">
-        <v>85</v>
-      </c>
-      <c r="I7" s="6">
-        <v>124</v>
-      </c>
-      <c r="J7" s="6">
-        <v>130</v>
-      </c>
-      <c r="K7" s="9">
-        <v>95</v>
-      </c>
-      <c r="L7" s="6">
-        <v>95</v>
-      </c>
-      <c r="M7" s="6">
-        <v>130</v>
-      </c>
-      <c r="N7" s="6">
-        <f>SUM($D7:$M7)</f>
-        <v>976</v>
-      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="16"/>
-      <c r="D8" s="9">
-        <v>10241</v>
-      </c>
-      <c r="E8" s="6">
-        <v>13400</v>
-      </c>
-      <c r="F8" s="6">
-        <v>22578</v>
-      </c>
-      <c r="G8" s="9">
-        <v>9980</v>
-      </c>
-      <c r="H8" s="6">
-        <v>15050</v>
-      </c>
-      <c r="I8" s="6">
-        <v>20200</v>
-      </c>
-      <c r="J8" s="6">
-        <v>21000</v>
-      </c>
-      <c r="K8" s="9">
-        <v>8690</v>
-      </c>
-      <c r="L8" s="6">
-        <v>10900</v>
-      </c>
-      <c r="M8" s="6">
-        <v>19000</v>
-      </c>
-      <c r="N8" s="6">
-        <f>SUM($D8:$M8)</f>
-        <v>151039</v>
-      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
-      <c r="D9" s="9">
-        <v>1104</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1210</v>
-      </c>
-      <c r="F9" s="6">
-        <v>1898</v>
-      </c>
-      <c r="G9" s="9">
-        <v>902</v>
-      </c>
-      <c r="H9" s="6">
-        <v>1050</v>
-      </c>
-      <c r="I9" s="6">
-        <v>1490</v>
-      </c>
-      <c r="J9" s="6">
-        <v>1520</v>
-      </c>
-      <c r="K9" s="9">
-        <v>1385</v>
-      </c>
-      <c r="L9" s="6">
-        <v>1140</v>
-      </c>
-      <c r="M9" s="6">
-        <v>1925</v>
-      </c>
-      <c r="N9" s="6">
-        <f>SUM($D9:$M9)</f>
-        <v>13624</v>
-      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
@@ -2093,13 +1976,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6">
-        <f>SUM($D10:$M10)</f>
+        <f>SUM(D10:M10)</f>
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="16"/>
@@ -2123,7 +2006,7 @@
         <v>18</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>13</v>
@@ -2135,28 +2018,28 @@
         <v>15</v>
       </c>
       <c r="G13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="N13" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2167,51 +2050,51 @@
         <v>10000</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D14" s="10">
-        <f>$B14/$N$8*$D$8</f>
-        <v>678.03679844278622</v>
+        <f>$B14/$N$6*$D$6</f>
+        <v>700</v>
       </c>
       <c r="E14" s="10">
-        <f>$B14/$N$8*$E$8</f>
-        <v>887.18807725157069</v>
+        <f>$B14/$N$6*$E$6</f>
+        <v>800</v>
       </c>
       <c r="F14" s="10">
-        <f>$B14/$N$8*$F$8</f>
-        <v>1494.8457021034301</v>
+        <f t="shared" ref="F14:M14" si="0">$B14/$N$6*$D$6</f>
+        <v>700</v>
       </c>
       <c r="G14" s="10">
-        <f>$B14/$N$8*$G$8</f>
-        <v>660.75649335602054</v>
+        <f t="shared" ref="G14:M14" si="1">$B14/$N$6*$E$6</f>
+        <v>800</v>
       </c>
       <c r="H14" s="10">
-        <f>$B14/$N$8*$H$8</f>
-        <v>996.43138527135363</v>
+        <f t="shared" ref="H14:M14" si="2">$B14/$N$6*$D$6</f>
+        <v>700</v>
       </c>
       <c r="I14" s="10">
-        <f>$B14/$N$8*$I$8</f>
-        <v>1337.4029224240096</v>
+        <f t="shared" ref="I14:M14" si="3">$B14/$N$6*$E$6</f>
+        <v>800</v>
       </c>
       <c r="J14" s="10">
-        <f>$B14/$N$8*$J$8</f>
-        <v>1390.3693747972377</v>
+        <f t="shared" ref="J14:M14" si="4">$B14/$N$6*$D$6</f>
+        <v>700</v>
       </c>
       <c r="K14" s="10">
-        <f>$B14/$N$8*$K$8</f>
-        <v>575.34808890419026</v>
+        <f t="shared" ref="K14:M14" si="5">$B14/$N$6*$E$6</f>
+        <v>800</v>
       </c>
       <c r="L14" s="10">
-        <f>$B14/$N$8*$L$8</f>
-        <v>721.6679135852329</v>
+        <f t="shared" ref="L14:M14" si="6">$B14/$N$6*$D$6</f>
+        <v>700</v>
       </c>
       <c r="M14" s="10">
-        <f>$B14/$N$8*$M$8</f>
-        <v>1257.9532438641675</v>
+        <f t="shared" ref="M14" si="7">$B14/$N$6*$E$6</f>
+        <v>800</v>
       </c>
       <c r="N14" s="10">
         <f>$B14-SUM($D14:$M14)</f>
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2222,7 +2105,7 @@
         <v>6000</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D15" s="10">
         <f>$B15/$N$6*$D$6</f>
@@ -2277,7 +2160,7 @@
         <v>600</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D16" s="10">
         <f>$B16/$N$6*$D$6</f>
@@ -2320,7 +2203,7 @@
         <v>84</v>
       </c>
       <c r="N16" s="10">
-        <f t="shared" ref="N16:N23" si="0">$B16-SUM($D16:$M16)</f>
+        <f t="shared" ref="N16:N23" si="8">$B16-SUM($D16:$M16)</f>
         <v>0</v>
       </c>
     </row>
@@ -2332,7 +2215,7 @@
         <v>150</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D17" s="10">
         <f>$B17/$N$6*$D$6</f>
@@ -2347,11 +2230,11 @@
         <v>18.75</v>
       </c>
       <c r="G17" s="10">
-        <f t="shared" ref="G17:G19" si="1">$B17/$N$6*$G$6</f>
+        <f t="shared" ref="G17:G19" si="9">$B17/$N$6*$G$6</f>
         <v>10.5</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" ref="H17:H19" si="2">$B17/$N$6*$H$6</f>
+        <f t="shared" ref="H17:H19" si="10">$B17/$N$6*$H$6</f>
         <v>12</v>
       </c>
       <c r="I17" s="10">
@@ -2375,7 +2258,7 @@
         <v>21</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -2387,7 +2270,7 @@
         <v>2400</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D18" s="10">
         <f>$B18/$N$6*$D$6</f>
@@ -2402,11 +2285,11 @@
         <v>300</v>
       </c>
       <c r="G18" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>168</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>192</v>
       </c>
       <c r="I18" s="10">
@@ -2430,7 +2313,7 @@
         <v>336</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -2442,7 +2325,7 @@
         <v>900</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D19" s="10">
         <f>$B19/$N$6*$D$6</f>
@@ -2457,11 +2340,11 @@
         <v>112.5</v>
       </c>
       <c r="G19" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>63</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>72</v>
       </c>
       <c r="I19" s="10">
@@ -2485,7 +2368,7 @@
         <v>126</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -2497,51 +2380,51 @@
         <v>1200</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D20" s="10">
-        <f>$B20/$N$9*$D$9</f>
-        <v>97.240164415736942</v>
+        <f>$B20/$N$6*$D$6</f>
+        <v>84</v>
       </c>
       <c r="E20" s="10">
-        <f>$B20/$N$9*$E$9</f>
-        <v>106.57662947739284</v>
+        <f>$B20/$N$6*$E$6</f>
+        <v>96</v>
       </c>
       <c r="F20" s="10">
-        <f>$B20/$N$9*$F$9</f>
-        <v>167.17557251908397</v>
+        <f t="shared" ref="F20:M20" si="11">$B20/$N$6*$D$6</f>
+        <v>84</v>
       </c>
       <c r="G20" s="10">
-        <f>$B20/$N$9*$G$9</f>
-        <v>79.448032883147391</v>
+        <f t="shared" ref="G20:M20" si="12">$B20/$N$6*$E$6</f>
+        <v>96</v>
       </c>
       <c r="H20" s="10">
-        <f>$B20/$N$9*$H$9</f>
-        <v>92.483852025836754</v>
+        <f t="shared" ref="H20:M20" si="13">$B20/$N$6*$D$6</f>
+        <v>84</v>
       </c>
       <c r="I20" s="10">
-        <f>$B20/$N$9*$I$9</f>
-        <v>131.23899001761598</v>
+        <f t="shared" ref="I20:M20" si="14">$B20/$N$6*$E$6</f>
+        <v>96</v>
       </c>
       <c r="J20" s="10">
-        <f>$B20/$N$9*$J$9</f>
-        <v>133.88138578978274</v>
+        <f t="shared" ref="J20:M20" si="15">$B20/$N$6*$D$6</f>
+        <v>84</v>
       </c>
       <c r="K20" s="10">
-        <f>$B20/$N$9*$K$9</f>
-        <v>121.9906048150323</v>
+        <f t="shared" ref="K20:M20" si="16">$B20/$N$6*$E$6</f>
+        <v>96</v>
       </c>
       <c r="L20" s="10">
-        <f>$B20/$N$9*$L$9</f>
-        <v>100.41103934233705</v>
+        <f t="shared" ref="L20:M20" si="17">$B20/$N$6*$D$6</f>
+        <v>84</v>
       </c>
       <c r="M20" s="10">
-        <f>$B20/$N$9*$M$9</f>
-        <v>169.55372871403407</v>
+        <f t="shared" ref="M20" si="18">$B20/$N$6*$E$6</f>
+        <v>96</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -2552,7 +2435,7 @@
         <v>1500</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D21" s="10">
         <f>$B21/$N$6*$D$6</f>
@@ -2595,7 +2478,7 @@
         <v>210</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -2607,7 +2490,7 @@
         <v>190</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D22" s="10">
         <f>$B22/$N$6*$D$6</f>
@@ -2650,7 +2533,7 @@
         <v>26.6</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -2705,7 +2588,7 @@
         <v>375</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -2720,47 +2603,47 @@
       <c r="C24" s="17"/>
       <c r="D24" s="11">
         <f>SUBTOTAL(109,D14:D23)</f>
-        <v>1972.0769628585231</v>
+        <v>1980.8</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" ref="E24:F24" si="3">SUBTOTAL(109,E14:E23)</f>
-        <v>2307.9647067289634</v>
+        <f t="shared" ref="E24:F24" si="19">SUBTOTAL(109,E14:E23)</f>
+        <v>2210.1999999999998</v>
       </c>
       <c r="F24" s="11">
-        <f t="shared" si="3"/>
-        <v>3504.5212746225143</v>
+        <f t="shared" si="19"/>
+        <v>2626.5</v>
       </c>
       <c r="G24" s="11">
         <f>SUBTOTAL(109,G14:G23)</f>
-        <v>1937.0045262391679</v>
+        <v>2092.8000000000002</v>
       </c>
       <c r="H24" s="11">
-        <f t="shared" ref="H24:J24" si="4">SUBTOTAL(109,H14:H23)</f>
-        <v>2403.1152372971901</v>
+        <f t="shared" ref="H24:J24" si="20">SUBTOTAL(109,H14:H23)</f>
+        <v>2098.1999999999998</v>
       </c>
       <c r="I24" s="11">
-        <f t="shared" si="4"/>
-        <v>3311.1419124416252</v>
+        <f t="shared" si="20"/>
+        <v>2738.5</v>
       </c>
       <c r="J24" s="11">
-        <f t="shared" si="4"/>
-        <v>3542.85076058702</v>
+        <f t="shared" si="20"/>
+        <v>2802.6</v>
       </c>
       <c r="K24" s="11">
         <f>SUBTOTAL(109,K14:K23)</f>
-        <v>2070.2386937192227</v>
+        <v>2268.9</v>
       </c>
       <c r="L24" s="11">
-        <f t="shared" ref="L24:M24" si="5">SUBTOTAL(109,L14:L23)</f>
-        <v>2194.9789529275699</v>
+        <f t="shared" ref="L24:M24" si="21">SUBTOTAL(109,L14:L23)</f>
+        <v>2156.9</v>
       </c>
       <c r="M24" s="11">
-        <f t="shared" si="5"/>
-        <v>3446.1069725782013</v>
+        <f t="shared" si="21"/>
+        <v>2914.6</v>
       </c>
       <c r="N24" s="13">
         <f>$B24-SUM($D24:$M24)</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2769,38 +2652,38 @@
       </c>
       <c r="B25" s="12">
         <f>SUM($D25:$M25)</f>
-        <v>-31800</v>
+        <v>-23500</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="12">
+        <v>-1500</v>
+      </c>
+      <c r="E25" s="12">
         <v>-2000</v>
       </c>
-      <c r="E25" s="12">
+      <c r="F25" s="12">
         <v>-3000</v>
       </c>
-      <c r="F25" s="12">
-        <v>-4200</v>
-      </c>
       <c r="G25" s="12">
+        <v>-1500</v>
+      </c>
+      <c r="H25" s="12">
         <v>-2000</v>
       </c>
-      <c r="H25" s="12">
+      <c r="I25" s="12">
         <v>-3000</v>
       </c>
-      <c r="I25" s="12">
-        <v>-4200</v>
-      </c>
       <c r="J25" s="12">
-        <v>-4200</v>
+        <v>-3000</v>
       </c>
       <c r="K25" s="12">
         <v>-2000</v>
       </c>
       <c r="L25" s="12">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="M25" s="12">
-        <v>-4200</v>
+        <v>-3500</v>
       </c>
       <c r="N25" s="12">
         <f>$B25-SUM($D25:$M25)</f>
@@ -2813,48 +2696,48 @@
       </c>
       <c r="B26" s="10">
         <f>SUM($D26:$M26)</f>
-        <v>-5110.0000000000018</v>
+        <v>389.99999999999977</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="10">
         <f>$D24+$D25</f>
-        <v>-27.923037141476925</v>
+        <v>480.79999999999995</v>
       </c>
       <c r="E26" s="10">
         <f>$E24+$E25</f>
-        <v>-692.03529327103661</v>
+        <v>210.19999999999982</v>
       </c>
       <c r="F26" s="10">
         <f>$F24+$F25</f>
-        <v>-695.47872537748572</v>
+        <v>-373.5</v>
       </c>
       <c r="G26" s="10">
         <f>$G24+$G25</f>
-        <v>-62.995473760832056</v>
+        <v>592.80000000000018</v>
       </c>
       <c r="H26" s="10">
         <f>$H24+$H25</f>
-        <v>-596.88476270280989</v>
+        <v>98.199999999999818</v>
       </c>
       <c r="I26" s="10">
         <f>$I24+$I25</f>
-        <v>-888.85808755837479</v>
+        <v>-261.5</v>
       </c>
       <c r="J26" s="10">
         <f>$J24+$J25</f>
-        <v>-657.14923941298002</v>
+        <v>-197.40000000000009</v>
       </c>
       <c r="K26" s="10">
         <f>$K24+$K25</f>
-        <v>70.238693719222738</v>
+        <v>268.90000000000009</v>
       </c>
       <c r="L26" s="10">
         <f>$L24+$L25</f>
-        <v>-805.02104707243006</v>
+        <v>156.90000000000009</v>
       </c>
       <c r="M26" s="10">
         <f>$M24+$M25</f>
-        <v>-753.89302742179871</v>
+        <v>-585.40000000000009</v>
       </c>
       <c r="N26" s="10">
         <f>$B26-SUM($D26:$M26)</f>
@@ -2863,57 +2746,57 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="6">
         <v>10</v>
       </c>
       <c r="C29" s="10">
-        <f>$F$24/12*10</f>
-        <v>2920.4343955187619</v>
+        <f>F24/12*10</f>
+        <v>2188.75</v>
       </c>
       <c r="D29" s="10">
-        <v>-3500</v>
+        <v>-2300</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" ref="E29:E30" si="6">$C29+$D29</f>
-        <v>-579.5656044812381</v>
+        <f t="shared" ref="E29:E30" si="22">$C29+$D29</f>
+        <v>-111.25</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="6">
         <v>2</v>
       </c>
       <c r="C30" s="10">
-        <f>$F$24/12*2</f>
-        <v>584.08687910375238</v>
+        <f>F24/12*2</f>
+        <v>437.75</v>
       </c>
       <c r="D30" s="10">
         <v>-700</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="6"/>
-        <v>-115.91312089624762</v>
+        <f t="shared" si="22"/>
+        <v>-262.25</v>
       </c>
     </row>
   </sheetData>
@@ -2927,22 +2810,25 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
   </mergeCells>
-  <conditionalFormatting sqref="D26:M26">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="E29:E30">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E29:E30">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="D26:M26">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="E20:M20 E14:M14" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
+++ b/realestate/documents/RipartizioneSpeseImmobiliariCondomini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\realestate\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CFDBED-0A4F-4269-9EF6-4F78BEA38C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A7DB7E-BFA2-476B-9D8D-59FF953DA9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{C8DA3664-E04A-4EE4-B0E8-18F2F24E5315}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="42">
   <si>
     <t>Riscaldamento</t>
   </si>
@@ -69,15 +69,6 @@
     <t>Tv</t>
   </si>
   <si>
-    <t>Acconti richiesti</t>
-  </si>
-  <si>
-    <t>Conguaglio spese</t>
-  </si>
-  <si>
-    <t>Spesa da ripartire</t>
-  </si>
-  <si>
     <t>App. 1</t>
   </si>
   <si>
@@ -99,9 +90,6 @@
     <t>Periodo:</t>
   </si>
   <si>
-    <t>Tipo di ripartizione</t>
-  </si>
-  <si>
     <t>altro</t>
   </si>
   <si>
@@ -166,6 +154,15 @@
   </si>
   <si>
     <t>Proprietario 2</t>
+  </si>
+  <si>
+    <t>Tipo di suddivisione</t>
+  </si>
+  <si>
+    <t>Spesa da suddividere</t>
+  </si>
+  <si>
+    <t>Anticipi richiesti</t>
   </si>
 </sst>
 </file>
@@ -367,27 +364,7 @@
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -787,17 +764,17 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2">
         <v>46023</v>
@@ -808,47 +785,47 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="21"/>
       <c r="D5" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="16"/>
@@ -889,7 +866,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="16"/>
@@ -907,7 +884,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="16"/>
@@ -925,7 +902,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
@@ -943,7 +920,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="16"/>
@@ -984,7 +961,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="16"/>
@@ -1002,46 +979,46 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="G13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="N13" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1052,46 +1029,46 @@
         <v>10000</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D14" s="10">
-        <f>$B14/$N$6*$D$6</f>
+        <f t="shared" ref="D14:D22" si="0">$B14/$N$6*$D$6</f>
         <v>700</v>
       </c>
       <c r="E14" s="10">
-        <f>$B14/$N$6*$E$6</f>
+        <f t="shared" ref="E14:E22" si="1">$B14/$N$6*$E$6</f>
         <v>800</v>
       </c>
       <c r="F14" s="10">
-        <f t="shared" ref="F14:M14" si="0">$B14/$N$6*$D$6</f>
+        <f t="shared" ref="F14" si="2">$B14/$N$6*$D$6</f>
         <v>700</v>
       </c>
       <c r="G14" s="10">
-        <f t="shared" ref="G14:M14" si="1">$B14/$N$6*$E$6</f>
+        <f t="shared" ref="G14" si="3">$B14/$N$6*$E$6</f>
         <v>800</v>
       </c>
       <c r="H14" s="10">
-        <f t="shared" ref="H14:M14" si="2">$B14/$N$6*$D$6</f>
+        <f t="shared" ref="H14" si="4">$B14/$N$6*$D$6</f>
         <v>700</v>
       </c>
       <c r="I14" s="10">
-        <f t="shared" ref="I14:M14" si="3">$B14/$N$6*$E$6</f>
+        <f t="shared" ref="I14" si="5">$B14/$N$6*$E$6</f>
         <v>800</v>
       </c>
       <c r="J14" s="10">
-        <f t="shared" ref="J14:M14" si="4">$B14/$N$6*$D$6</f>
+        <f t="shared" ref="J14" si="6">$B14/$N$6*$D$6</f>
         <v>700</v>
       </c>
       <c r="K14" s="10">
-        <f t="shared" ref="K14:M14" si="5">$B14/$N$6*$E$6</f>
+        <f t="shared" ref="K14" si="7">$B14/$N$6*$E$6</f>
         <v>800</v>
       </c>
       <c r="L14" s="10">
-        <f t="shared" ref="L14:M14" si="6">$B14/$N$6*$D$6</f>
+        <f t="shared" ref="L14" si="8">$B14/$N$6*$D$6</f>
         <v>700</v>
       </c>
       <c r="M14" s="10">
-        <f t="shared" ref="M14" si="7">$B14/$N$6*$E$6</f>
+        <f t="shared" ref="M14" si="9">$B14/$N$6*$E$6</f>
         <v>800</v>
       </c>
       <c r="N14" s="10">
@@ -1107,14 +1084,14 @@
         <v>6000</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D15" s="10">
-        <f>$B15/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>420</v>
       </c>
       <c r="E15" s="10">
-        <f>$B15/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>480</v>
       </c>
       <c r="F15" s="10">
@@ -1162,14 +1139,14 @@
         <v>600</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D16" s="10">
-        <f>$B16/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="E16" s="10">
-        <f>$B16/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="F16" s="10">
@@ -1205,7 +1182,7 @@
         <v>84</v>
       </c>
       <c r="N16" s="10">
-        <f t="shared" ref="N16:N23" si="8">$B16-SUM($D16:$M16)</f>
+        <f t="shared" ref="N16:N23" si="10">$B16-SUM($D16:$M16)</f>
         <v>0</v>
       </c>
     </row>
@@ -1217,14 +1194,14 @@
         <v>150</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D17" s="10">
-        <f>$B17/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
       <c r="E17" s="10">
-        <f>$B17/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="F17" s="10">
@@ -1232,11 +1209,11 @@
         <v>18.75</v>
       </c>
       <c r="G17" s="10">
-        <f t="shared" ref="G17:G19" si="9">$B17/$N$6*$G$6</f>
+        <f t="shared" ref="G17:G19" si="11">$B17/$N$6*$G$6</f>
         <v>10.5</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" ref="H17:H19" si="10">$B17/$N$6*$H$6</f>
+        <f t="shared" ref="H17:H19" si="12">$B17/$N$6*$H$6</f>
         <v>12</v>
       </c>
       <c r="I17" s="10">
@@ -1260,7 +1237,7 @@
         <v>21</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -1272,14 +1249,14 @@
         <v>2400</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D18" s="10">
-        <f>$B18/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>168</v>
       </c>
       <c r="E18" s="10">
-        <f>$B18/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>192</v>
       </c>
       <c r="F18" s="10">
@@ -1287,11 +1264,11 @@
         <v>300</v>
       </c>
       <c r="G18" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>168</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>192</v>
       </c>
       <c r="I18" s="10">
@@ -1315,7 +1292,7 @@
         <v>336</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -1327,14 +1304,14 @@
         <v>900</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D19" s="10">
-        <f>$B19/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="E19" s="10">
-        <f>$B19/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="F19" s="10">
@@ -1342,11 +1319,11 @@
         <v>112.5</v>
       </c>
       <c r="G19" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>63</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>72</v>
       </c>
       <c r="I19" s="10">
@@ -1370,7 +1347,7 @@
         <v>126</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -1382,50 +1359,50 @@
         <v>1200</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D20" s="10">
-        <f>$B20/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="E20" s="10">
-        <f>$B20/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="F20" s="10">
-        <f t="shared" ref="F20:M20" si="11">$B20/$N$6*$D$6</f>
+        <f t="shared" ref="F20" si="13">$B20/$N$6*$D$6</f>
         <v>84</v>
       </c>
       <c r="G20" s="10">
-        <f t="shared" ref="G20:M20" si="12">$B20/$N$6*$E$6</f>
+        <f t="shared" ref="G20" si="14">$B20/$N$6*$E$6</f>
         <v>96</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" ref="H20:M20" si="13">$B20/$N$6*$D$6</f>
+        <f t="shared" ref="H20" si="15">$B20/$N$6*$D$6</f>
         <v>84</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" ref="I20:M20" si="14">$B20/$N$6*$E$6</f>
+        <f t="shared" ref="I20" si="16">$B20/$N$6*$E$6</f>
         <v>96</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" ref="J20:M20" si="15">$B20/$N$6*$D$6</f>
+        <f t="shared" ref="J20" si="17">$B20/$N$6*$D$6</f>
         <v>84</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" ref="K20:M20" si="16">$B20/$N$6*$E$6</f>
+        <f t="shared" ref="K20" si="18">$B20/$N$6*$E$6</f>
         <v>96</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" ref="L20:M20" si="17">$B20/$N$6*$D$6</f>
+        <f t="shared" ref="L20" si="19">$B20/$N$6*$D$6</f>
         <v>84</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" ref="M20" si="18">$B20/$N$6*$E$6</f>
+        <f t="shared" ref="M20" si="20">$B20/$N$6*$E$6</f>
         <v>96</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>300</v>
       </c>
     </row>
@@ -1437,14 +1414,14 @@
         <v>1500</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D21" s="10">
-        <f>$B21/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="E21" s="10">
-        <f>$B21/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="F21" s="10">
@@ -1480,7 +1457,7 @@
         <v>210</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -1492,14 +1469,14 @@
         <v>190</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D22" s="10">
-        <f>$B22/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>13.3</v>
       </c>
       <c r="E22" s="10">
-        <f>$B22/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>15.2</v>
       </c>
       <c r="F22" s="10">
@@ -1535,7 +1512,7 @@
         <v>26.6</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -1547,7 +1524,7 @@
         <v>3750</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D23" s="10">
         <f>$B23/$N$10*$D$10</f>
@@ -1590,13 +1567,13 @@
         <v>375</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B24" s="11">
         <f>SUBTOTAL(109,B14:B23)</f>
@@ -1608,11 +1585,11 @@
         <v>1980.8</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" ref="E24:F24" si="19">SUBTOTAL(109,E14:E23)</f>
+        <f t="shared" ref="E24:F24" si="21">SUBTOTAL(109,E14:E23)</f>
         <v>2210.1999999999998</v>
       </c>
       <c r="F24" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2626.5</v>
       </c>
       <c r="G24" s="11">
@@ -1620,15 +1597,15 @@
         <v>2092.8000000000002</v>
       </c>
       <c r="H24" s="11">
-        <f t="shared" ref="H24:J24" si="20">SUBTOTAL(109,H14:H23)</f>
+        <f t="shared" ref="H24:J24" si="22">SUBTOTAL(109,H14:H23)</f>
         <v>2098.1999999999998</v>
       </c>
       <c r="I24" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2738.5</v>
       </c>
       <c r="J24" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2802.6</v>
       </c>
       <c r="K24" s="11">
@@ -1636,11 +1613,11 @@
         <v>2268.9</v>
       </c>
       <c r="L24" s="11">
-        <f t="shared" ref="L24:M24" si="21">SUBTOTAL(109,L14:L23)</f>
+        <f t="shared" ref="L24:M24" si="23">SUBTOTAL(109,L14:L23)</f>
         <v>2156.9</v>
       </c>
       <c r="M24" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2914.6</v>
       </c>
       <c r="N24" s="13">
@@ -1650,7 +1627,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B25" s="12">
         <f>SUM($D25:$M25)</f>
@@ -1694,7 +1671,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B26" s="10">
         <f>SUM($D26:$M26)</f>
@@ -1758,10 +1735,10 @@
     <mergeCell ref="A10:C10"/>
   </mergeCells>
   <conditionalFormatting sqref="D26:M26">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1785,17 +1762,17 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2">
         <v>46023</v>
@@ -1806,47 +1783,47 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="21"/>
       <c r="D5" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="16"/>
@@ -1887,7 +1864,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="16"/>
@@ -1905,7 +1882,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="16"/>
@@ -1923,7 +1900,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
@@ -1941,7 +1918,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="16"/>
@@ -1982,7 +1959,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="16"/>
@@ -2000,46 +1977,46 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="G13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="N13" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2050,46 +2027,46 @@
         <v>10000</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D14" s="10">
-        <f>$B14/$N$6*$D$6</f>
+        <f t="shared" ref="D14:D22" si="0">$B14/$N$6*$D$6</f>
         <v>700</v>
       </c>
       <c r="E14" s="10">
-        <f>$B14/$N$6*$E$6</f>
+        <f t="shared" ref="E14:E22" si="1">$B14/$N$6*$E$6</f>
         <v>800</v>
       </c>
       <c r="F14" s="10">
-        <f t="shared" ref="F14:M14" si="0">$B14/$N$6*$D$6</f>
+        <f t="shared" ref="F14" si="2">$B14/$N$6*$D$6</f>
         <v>700</v>
       </c>
       <c r="G14" s="10">
-        <f t="shared" ref="G14:M14" si="1">$B14/$N$6*$E$6</f>
+        <f t="shared" ref="G14" si="3">$B14/$N$6*$E$6</f>
         <v>800</v>
       </c>
       <c r="H14" s="10">
-        <f t="shared" ref="H14:M14" si="2">$B14/$N$6*$D$6</f>
+        <f t="shared" ref="H14" si="4">$B14/$N$6*$D$6</f>
         <v>700</v>
       </c>
       <c r="I14" s="10">
-        <f t="shared" ref="I14:M14" si="3">$B14/$N$6*$E$6</f>
+        <f t="shared" ref="I14" si="5">$B14/$N$6*$E$6</f>
         <v>800</v>
       </c>
       <c r="J14" s="10">
-        <f t="shared" ref="J14:M14" si="4">$B14/$N$6*$D$6</f>
+        <f t="shared" ref="J14" si="6">$B14/$N$6*$D$6</f>
         <v>700</v>
       </c>
       <c r="K14" s="10">
-        <f t="shared" ref="K14:M14" si="5">$B14/$N$6*$E$6</f>
+        <f t="shared" ref="K14" si="7">$B14/$N$6*$E$6</f>
         <v>800</v>
       </c>
       <c r="L14" s="10">
-        <f t="shared" ref="L14:M14" si="6">$B14/$N$6*$D$6</f>
+        <f t="shared" ref="L14" si="8">$B14/$N$6*$D$6</f>
         <v>700</v>
       </c>
       <c r="M14" s="10">
-        <f t="shared" ref="M14" si="7">$B14/$N$6*$E$6</f>
+        <f t="shared" ref="M14" si="9">$B14/$N$6*$E$6</f>
         <v>800</v>
       </c>
       <c r="N14" s="10">
@@ -2105,14 +2082,14 @@
         <v>6000</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D15" s="10">
-        <f>$B15/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>420</v>
       </c>
       <c r="E15" s="10">
-        <f>$B15/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>480</v>
       </c>
       <c r="F15" s="10">
@@ -2160,14 +2137,14 @@
         <v>600</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D16" s="10">
-        <f>$B16/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="E16" s="10">
-        <f>$B16/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="F16" s="10">
@@ -2203,7 +2180,7 @@
         <v>84</v>
       </c>
       <c r="N16" s="10">
-        <f t="shared" ref="N16:N23" si="8">$B16-SUM($D16:$M16)</f>
+        <f t="shared" ref="N16:N23" si="10">$B16-SUM($D16:$M16)</f>
         <v>0</v>
       </c>
     </row>
@@ -2215,14 +2192,14 @@
         <v>150</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D17" s="10">
-        <f>$B17/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
       <c r="E17" s="10">
-        <f>$B17/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="F17" s="10">
@@ -2230,11 +2207,11 @@
         <v>18.75</v>
       </c>
       <c r="G17" s="10">
-        <f t="shared" ref="G17:G19" si="9">$B17/$N$6*$G$6</f>
+        <f t="shared" ref="G17:G19" si="11">$B17/$N$6*$G$6</f>
         <v>10.5</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" ref="H17:H19" si="10">$B17/$N$6*$H$6</f>
+        <f t="shared" ref="H17:H19" si="12">$B17/$N$6*$H$6</f>
         <v>12</v>
       </c>
       <c r="I17" s="10">
@@ -2258,7 +2235,7 @@
         <v>21</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -2270,14 +2247,14 @@
         <v>2400</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D18" s="10">
-        <f>$B18/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>168</v>
       </c>
       <c r="E18" s="10">
-        <f>$B18/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>192</v>
       </c>
       <c r="F18" s="10">
@@ -2285,11 +2262,11 @@
         <v>300</v>
       </c>
       <c r="G18" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>168</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>192</v>
       </c>
       <c r="I18" s="10">
@@ -2313,7 +2290,7 @@
         <v>336</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -2325,14 +2302,14 @@
         <v>900</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D19" s="10">
-        <f>$B19/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="E19" s="10">
-        <f>$B19/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="F19" s="10">
@@ -2340,11 +2317,11 @@
         <v>112.5</v>
       </c>
       <c r="G19" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>63</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>72</v>
       </c>
       <c r="I19" s="10">
@@ -2368,7 +2345,7 @@
         <v>126</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -2380,50 +2357,50 @@
         <v>1200</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D20" s="10">
-        <f>$B20/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="E20" s="10">
-        <f>$B20/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="F20" s="10">
-        <f t="shared" ref="F20:M20" si="11">$B20/$N$6*$D$6</f>
+        <f t="shared" ref="F20" si="13">$B20/$N$6*$D$6</f>
         <v>84</v>
       </c>
       <c r="G20" s="10">
-        <f t="shared" ref="G20:M20" si="12">$B20/$N$6*$E$6</f>
+        <f t="shared" ref="G20" si="14">$B20/$N$6*$E$6</f>
         <v>96</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" ref="H20:M20" si="13">$B20/$N$6*$D$6</f>
+        <f t="shared" ref="H20" si="15">$B20/$N$6*$D$6</f>
         <v>84</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" ref="I20:M20" si="14">$B20/$N$6*$E$6</f>
+        <f t="shared" ref="I20" si="16">$B20/$N$6*$E$6</f>
         <v>96</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" ref="J20:M20" si="15">$B20/$N$6*$D$6</f>
+        <f t="shared" ref="J20" si="17">$B20/$N$6*$D$6</f>
         <v>84</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" ref="K20:M20" si="16">$B20/$N$6*$E$6</f>
+        <f t="shared" ref="K20" si="18">$B20/$N$6*$E$6</f>
         <v>96</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" ref="L20:M20" si="17">$B20/$N$6*$D$6</f>
+        <f t="shared" ref="L20" si="19">$B20/$N$6*$D$6</f>
         <v>84</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" ref="M20" si="18">$B20/$N$6*$E$6</f>
+        <f t="shared" ref="M20" si="20">$B20/$N$6*$E$6</f>
         <v>96</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>300</v>
       </c>
     </row>
@@ -2435,14 +2412,14 @@
         <v>1500</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D21" s="10">
-        <f>$B21/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="E21" s="10">
-        <f>$B21/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="F21" s="10">
@@ -2478,7 +2455,7 @@
         <v>210</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -2490,14 +2467,14 @@
         <v>190</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D22" s="10">
-        <f>$B22/$N$6*$D$6</f>
+        <f t="shared" si="0"/>
         <v>13.3</v>
       </c>
       <c r="E22" s="10">
-        <f>$B22/$N$6*$E$6</f>
+        <f t="shared" si="1"/>
         <v>15.2</v>
       </c>
       <c r="F22" s="10">
@@ -2533,7 +2510,7 @@
         <v>26.6</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -2545,7 +2522,7 @@
         <v>3750</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D23" s="10">
         <f>$B23/$N$10*$D$10</f>
@@ -2588,13 +2565,13 @@
         <v>375</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B24" s="11">
         <f>SUBTOTAL(109,B14:B23)</f>
@@ -2606,11 +2583,11 @@
         <v>1980.8</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" ref="E24:F24" si="19">SUBTOTAL(109,E14:E23)</f>
+        <f t="shared" ref="E24:F24" si="21">SUBTOTAL(109,E14:E23)</f>
         <v>2210.1999999999998</v>
       </c>
       <c r="F24" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2626.5</v>
       </c>
       <c r="G24" s="11">
@@ -2618,15 +2595,15 @@
         <v>2092.8000000000002</v>
       </c>
       <c r="H24" s="11">
-        <f t="shared" ref="H24:J24" si="20">SUBTOTAL(109,H14:H23)</f>
+        <f t="shared" ref="H24:J24" si="22">SUBTOTAL(109,H14:H23)</f>
         <v>2098.1999999999998</v>
       </c>
       <c r="I24" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2738.5</v>
       </c>
       <c r="J24" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2802.6</v>
       </c>
       <c r="K24" s="11">
@@ -2634,11 +2611,11 @@
         <v>2268.9</v>
       </c>
       <c r="L24" s="11">
-        <f t="shared" ref="L24:M24" si="21">SUBTOTAL(109,L14:L23)</f>
+        <f t="shared" ref="L24:M24" si="23">SUBTOTAL(109,L14:L23)</f>
         <v>2156.9</v>
       </c>
       <c r="M24" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2914.6</v>
       </c>
       <c r="N24" s="13">
@@ -2648,7 +2625,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B25" s="12">
         <f>SUM($D25:$M25)</f>
@@ -2692,7 +2669,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B26" s="10">
         <f>SUM($D26:$M26)</f>
@@ -2746,24 +2723,24 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B29" s="6">
         <v>10</v>
@@ -2776,13 +2753,13 @@
         <v>-2300</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" ref="E29:E30" si="22">$C29+$D29</f>
+        <f t="shared" ref="E29:E30" si="24">$C29+$D29</f>
         <v>-111.25</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B30" s="6">
         <v>2</v>
@@ -2795,7 +2772,7 @@
         <v>-700</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-262.25</v>
       </c>
     </row>
@@ -2810,19 +2787,19 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
   </mergeCells>
-  <conditionalFormatting sqref="E29:E30">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThan">
+  <conditionalFormatting sqref="D26:M26">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D26:M26">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="E29:E30">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
